--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119548947</v>
+        <v>119548823</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,47 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480500</v>
+        <v>480140</v>
       </c>
       <c r="R5" t="n">
-        <v>6826464</v>
+        <v>6827088</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119548715</v>
+        <v>119548820</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480513</v>
+        <v>480136</v>
       </c>
       <c r="R6" t="n">
-        <v>6826505</v>
+        <v>6826965</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119548717</v>
+        <v>119548850</v>
       </c>
       <c r="B7" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480157</v>
+        <v>480253</v>
       </c>
       <c r="R7" t="n">
-        <v>6827091</v>
+        <v>6826941</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119548823</v>
+        <v>119548891</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1336,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480140</v>
+        <v>480461</v>
       </c>
       <c r="R8" t="n">
-        <v>6827088</v>
+        <v>6826839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119548820</v>
+        <v>119548875</v>
       </c>
       <c r="B9" t="n">
         <v>78526</v>
@@ -1438,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480136</v>
+        <v>480351</v>
       </c>
       <c r="R9" t="n">
-        <v>6826965</v>
+        <v>6826904</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119548850</v>
+        <v>119548816</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1540,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480253</v>
+        <v>480158</v>
       </c>
       <c r="R10" t="n">
-        <v>6826941</v>
+        <v>6826964</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119548891</v>
+        <v>119548802</v>
       </c>
       <c r="B11" t="n">
         <v>78526</v>
@@ -1642,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480461</v>
+        <v>480332</v>
       </c>
       <c r="R11" t="n">
-        <v>6826839</v>
+        <v>6826852</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119548875</v>
+        <v>119548947</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,38 +1707,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480351</v>
+        <v>480500</v>
       </c>
       <c r="R12" t="n">
-        <v>6826904</v>
+        <v>6826464</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119548816</v>
+        <v>119548652</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480158</v>
+        <v>480499</v>
       </c>
       <c r="R13" t="n">
-        <v>6826964</v>
+        <v>6826449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119548802</v>
+        <v>119548715</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480332</v>
+        <v>480513</v>
       </c>
       <c r="R14" t="n">
-        <v>6826852</v>
+        <v>6826505</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119548652</v>
+        <v>119548717</v>
       </c>
       <c r="B15" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480499</v>
+        <v>480157</v>
       </c>
       <c r="R15" t="n">
-        <v>6826449</v>
+        <v>6827091</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3261,10 +3261,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119548949</v>
+        <v>119548625</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3273,47 +3273,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480515</v>
+        <v>480496</v>
       </c>
       <c r="R27" t="n">
-        <v>6826517</v>
+        <v>6826771</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,7 +3363,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119548969</v>
+        <v>119548949</v>
       </c>
       <c r="B28" t="n">
         <v>91840</v>
@@ -3405,17 +3396,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480390</v>
+        <v>480515</v>
       </c>
       <c r="R28" t="n">
-        <v>6826677</v>
+        <v>6826517</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119548964</v>
+        <v>119548969</v>
       </c>
       <c r="B29" t="n">
         <v>91840</v>
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480219</v>
+        <v>480390</v>
       </c>
       <c r="R29" t="n">
-        <v>6826902</v>
+        <v>6826677</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3576,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119548736</v>
+        <v>119548964</v>
       </c>
       <c r="B30" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3588,25 +3588,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480143</v>
+        <v>480219</v>
       </c>
       <c r="R30" t="n">
-        <v>6826960</v>
+        <v>6826902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119548693</v>
+        <v>119548897</v>
       </c>
       <c r="B31" t="n">
-        <v>79115</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3694,21 +3694,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480405</v>
+        <v>480504</v>
       </c>
       <c r="R31" t="n">
-        <v>6826710</v>
+        <v>6826757</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119548625</v>
+        <v>119548790</v>
       </c>
       <c r="B32" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480496</v>
+        <v>480589</v>
       </c>
       <c r="R32" t="n">
-        <v>6826771</v>
+        <v>6826666</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119548897</v>
+        <v>119548884</v>
       </c>
       <c r="B33" t="n">
         <v>78526</v>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480504</v>
+        <v>480384</v>
       </c>
       <c r="R33" t="n">
-        <v>6826757</v>
+        <v>6826819</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119548790</v>
+        <v>119548716</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4000,21 +4000,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480589</v>
+        <v>480133</v>
       </c>
       <c r="R34" t="n">
-        <v>6826666</v>
+        <v>6827087</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119548884</v>
+        <v>119548970</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4098,25 +4098,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480384</v>
+        <v>480502</v>
       </c>
       <c r="R35" t="n">
-        <v>6826819</v>
+        <v>6826561</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119548970</v>
+        <v>119548736</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4200,25 +4200,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480502</v>
+        <v>480143</v>
       </c>
       <c r="R36" t="n">
-        <v>6826561</v>
+        <v>6826960</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119548716</v>
+        <v>119548693</v>
       </c>
       <c r="B37" t="n">
-        <v>91884</v>
+        <v>79115</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480133</v>
+        <v>480405</v>
       </c>
       <c r="R37" t="n">
-        <v>6827087</v>
+        <v>6826710</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -6144,7 +6144,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119548847</v>
+        <v>119548883</v>
       </c>
       <c r="B55" t="n">
         <v>78526</v>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480237</v>
+        <v>480363</v>
       </c>
       <c r="R55" t="n">
-        <v>6826952</v>
+        <v>6826853</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6246,7 +6246,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119548883</v>
+        <v>119548804</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480363</v>
+        <v>480313</v>
       </c>
       <c r="R56" t="n">
-        <v>6826853</v>
+        <v>6826915</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6348,7 +6348,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119548804</v>
+        <v>119548845</v>
       </c>
       <c r="B57" t="n">
         <v>78526</v>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480313</v>
+        <v>480275</v>
       </c>
       <c r="R57" t="n">
-        <v>6826915</v>
+        <v>6826975</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119548845</v>
+        <v>119548842</v>
       </c>
       <c r="B58" t="n">
         <v>78526</v>
@@ -6490,10 +6490,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480275</v>
+        <v>480268</v>
       </c>
       <c r="R58" t="n">
-        <v>6826975</v>
+        <v>6826985</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119548951</v>
+        <v>119548657</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6666,47 +6666,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480122</v>
+        <v>480103</v>
       </c>
       <c r="R60" t="n">
-        <v>6827072</v>
+        <v>6827016</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6765,10 +6756,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119548975</v>
+        <v>119548847</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6777,47 +6768,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480174</v>
+        <v>480237</v>
       </c>
       <c r="R61" t="n">
-        <v>6827070</v>
+        <v>6826952</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6876,7 +6858,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119548934</v>
+        <v>119548951</v>
       </c>
       <c r="B62" t="n">
         <v>91840</v>
@@ -6911,7 +6893,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6925,10 +6907,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480127</v>
+        <v>480122</v>
       </c>
       <c r="R62" t="n">
-        <v>6826954</v>
+        <v>6827072</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6987,7 +6969,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119548977</v>
+        <v>119548975</v>
       </c>
       <c r="B63" t="n">
         <v>91840</v>
@@ -7020,17 +7002,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480512</v>
+        <v>480174</v>
       </c>
       <c r="R63" t="n">
-        <v>6826505</v>
+        <v>6827070</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7089,10 +7080,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119548657</v>
+        <v>119548934</v>
       </c>
       <c r="B64" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7101,38 +7092,47 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480103</v>
+        <v>480127</v>
       </c>
       <c r="R64" t="n">
-        <v>6827016</v>
+        <v>6826954</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7191,10 +7191,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119548704</v>
+        <v>119548977</v>
       </c>
       <c r="B65" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7203,25 +7203,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480161</v>
+        <v>480512</v>
       </c>
       <c r="R65" t="n">
-        <v>6827018</v>
+        <v>6826505</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7293,7 +7293,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119548700</v>
+        <v>119548704</v>
       </c>
       <c r="B66" t="n">
         <v>57463</v>
@@ -7326,21 +7326,17 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480482</v>
+        <v>480161</v>
       </c>
       <c r="R66" t="n">
-        <v>6826326</v>
+        <v>6827018</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7399,10 +7395,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119548842</v>
+        <v>119548700</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7415,34 +7411,38 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480268</v>
+        <v>480482</v>
       </c>
       <c r="R67" t="n">
-        <v>6826985</v>
+        <v>6826326</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8632,10 +8632,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119548663</v>
+        <v>119548826</v>
       </c>
       <c r="B79" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8648,21 +8648,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480362</v>
+        <v>480183</v>
       </c>
       <c r="R79" t="n">
-        <v>6826679</v>
+        <v>6827072</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8734,10 +8734,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119548654</v>
+        <v>119548926</v>
       </c>
       <c r="B80" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8750,21 +8750,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8774,10 +8774,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480304</v>
+        <v>480486</v>
       </c>
       <c r="R80" t="n">
-        <v>6826831</v>
+        <v>6826356</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8836,10 +8836,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119548733</v>
+        <v>119548877</v>
       </c>
       <c r="B81" t="n">
-        <v>91863</v>
+        <v>78526</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8852,21 +8852,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8876,10 +8876,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480276</v>
+        <v>480382</v>
       </c>
       <c r="R81" t="n">
-        <v>6826945</v>
+        <v>6826884</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8938,10 +8938,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119548610</v>
+        <v>119548840</v>
       </c>
       <c r="B82" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8954,21 +8954,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8978,10 +8978,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480250</v>
+        <v>480239</v>
       </c>
       <c r="R82" t="n">
-        <v>6826939</v>
+        <v>6827010</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9040,7 +9040,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119548826</v>
+        <v>119548864</v>
       </c>
       <c r="B83" t="n">
         <v>78526</v>
@@ -9080,10 +9080,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480183</v>
+        <v>480328</v>
       </c>
       <c r="R83" t="n">
-        <v>6827072</v>
+        <v>6826958</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9142,7 +9142,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119548926</v>
+        <v>119548789</v>
       </c>
       <c r="B84" t="n">
         <v>78526</v>
@@ -9182,10 +9182,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480486</v>
+        <v>480577</v>
       </c>
       <c r="R84" t="n">
-        <v>6826356</v>
+        <v>6826648</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9244,7 +9244,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119548877</v>
+        <v>119548801</v>
       </c>
       <c r="B85" t="n">
         <v>78526</v>
@@ -9284,10 +9284,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480382</v>
+        <v>480314</v>
       </c>
       <c r="R85" t="n">
-        <v>6826884</v>
+        <v>6826847</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9346,7 +9346,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119548840</v>
+        <v>119548841</v>
       </c>
       <c r="B86" t="n">
         <v>78526</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>480239</v>
+        <v>480248</v>
       </c>
       <c r="R86" t="n">
-        <v>6827010</v>
+        <v>6827000</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9448,10 +9448,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119548864</v>
+        <v>119548702</v>
       </c>
       <c r="B87" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9464,21 +9464,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>480328</v>
+        <v>480103</v>
       </c>
       <c r="R87" t="n">
-        <v>6826958</v>
+        <v>6827007</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9550,10 +9550,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119548789</v>
+        <v>119548733</v>
       </c>
       <c r="B88" t="n">
-        <v>78526</v>
+        <v>91863</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9566,21 +9566,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9590,10 +9590,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>480577</v>
+        <v>480276</v>
       </c>
       <c r="R88" t="n">
-        <v>6826648</v>
+        <v>6826945</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9652,10 +9652,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119548801</v>
+        <v>119548610</v>
       </c>
       <c r="B89" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9668,21 +9668,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9692,10 +9692,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>480314</v>
+        <v>480250</v>
       </c>
       <c r="R89" t="n">
-        <v>6826847</v>
+        <v>6826939</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9754,10 +9754,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119548841</v>
+        <v>119548962</v>
       </c>
       <c r="B90" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9766,25 +9766,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9794,10 +9794,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>480248</v>
+        <v>480349</v>
       </c>
       <c r="R90" t="n">
-        <v>6827000</v>
+        <v>6826879</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9856,7 +9856,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119548962</v>
+        <v>119548955</v>
       </c>
       <c r="B91" t="n">
         <v>91840</v>
@@ -9889,17 +9889,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>480349</v>
+        <v>480224</v>
       </c>
       <c r="R91" t="n">
-        <v>6826879</v>
+        <v>6827082</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9958,7 +9967,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119548955</v>
+        <v>119548954</v>
       </c>
       <c r="B92" t="n">
         <v>91840</v>
@@ -9993,7 +10002,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10007,10 +10016,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>480224</v>
+        <v>480107</v>
       </c>
       <c r="R92" t="n">
-        <v>6827082</v>
+        <v>6826990</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10069,10 +10078,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119548954</v>
+        <v>119548663</v>
       </c>
       <c r="B93" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10081,47 +10090,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>480107</v>
+        <v>480362</v>
       </c>
       <c r="R93" t="n">
-        <v>6826990</v>
+        <v>6826679</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10180,10 +10180,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119548702</v>
+        <v>119548654</v>
       </c>
       <c r="B94" t="n">
-        <v>57463</v>
+        <v>79144</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10196,21 +10196,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>480103</v>
+        <v>480304</v>
       </c>
       <c r="R94" t="n">
-        <v>6827007</v>
+        <v>6826831</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11617,10 +11617,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119548896</v>
+        <v>119548628</v>
       </c>
       <c r="B108" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11633,21 +11633,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>480491</v>
+        <v>480474</v>
       </c>
       <c r="R108" t="n">
-        <v>6826791</v>
+        <v>6826656</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11719,10 +11719,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119548807</v>
+        <v>119548709</v>
       </c>
       <c r="B109" t="n">
-        <v>78526</v>
+        <v>91463</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11735,21 +11735,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11759,10 +11759,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>480283</v>
+        <v>480356</v>
       </c>
       <c r="R109" t="n">
-        <v>6826928</v>
+        <v>6826904</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11821,10 +11821,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119548846</v>
+        <v>119548708</v>
       </c>
       <c r="B110" t="n">
-        <v>78526</v>
+        <v>91463</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11837,21 +11837,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11861,10 +11861,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>480249</v>
+        <v>480127</v>
       </c>
       <c r="R110" t="n">
-        <v>6826968</v>
+        <v>6826974</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11923,10 +11923,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119548796</v>
+        <v>119548727</v>
       </c>
       <c r="B111" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11935,25 +11935,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11963,10 +11963,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>480409</v>
+        <v>480224</v>
       </c>
       <c r="R111" t="n">
-        <v>6826806</v>
+        <v>6827082</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12025,7 +12025,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119548873</v>
+        <v>119548896</v>
       </c>
       <c r="B112" t="n">
         <v>78526</v>
@@ -12065,10 +12065,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>480356</v>
+        <v>480491</v>
       </c>
       <c r="R112" t="n">
-        <v>6826918</v>
+        <v>6826791</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12127,7 +12127,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119548878</v>
+        <v>119548807</v>
       </c>
       <c r="B113" t="n">
         <v>78526</v>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>480370</v>
+        <v>480283</v>
       </c>
       <c r="R113" t="n">
-        <v>6826883</v>
+        <v>6826928</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12229,7 +12229,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119548815</v>
+        <v>119548846</v>
       </c>
       <c r="B114" t="n">
         <v>78526</v>
@@ -12269,10 +12269,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>480163</v>
+        <v>480249</v>
       </c>
       <c r="R114" t="n">
-        <v>6826956</v>
+        <v>6826968</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12331,10 +12331,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119548628</v>
+        <v>119548796</v>
       </c>
       <c r="B115" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12347,21 +12347,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>480474</v>
+        <v>480409</v>
       </c>
       <c r="R115" t="n">
-        <v>6826656</v>
+        <v>6826806</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12433,10 +12433,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119548709</v>
+        <v>119548873</v>
       </c>
       <c r="B116" t="n">
-        <v>91463</v>
+        <v>78526</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12449,21 +12449,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12476,7 +12476,7 @@
         <v>480356</v>
       </c>
       <c r="R116" t="n">
-        <v>6826904</v>
+        <v>6826918</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12535,10 +12535,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119548708</v>
+        <v>119548878</v>
       </c>
       <c r="B117" t="n">
-        <v>91463</v>
+        <v>78526</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12551,21 +12551,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12575,10 +12575,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>480127</v>
+        <v>480370</v>
       </c>
       <c r="R117" t="n">
-        <v>6826974</v>
+        <v>6826883</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12637,10 +12637,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119548727</v>
+        <v>119548815</v>
       </c>
       <c r="B118" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12649,25 +12649,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12677,10 +12677,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>480224</v>
+        <v>480163</v>
       </c>
       <c r="R118" t="n">
-        <v>6827082</v>
+        <v>6826956</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15418,10 +15418,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119548996</v>
+        <v>119548604</v>
       </c>
       <c r="B145" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15434,21 +15434,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15458,10 +15458,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>480115</v>
+        <v>480319</v>
       </c>
       <c r="R145" t="n">
-        <v>6827003</v>
+        <v>6826923</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15520,7 +15520,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119548604</v>
+        <v>119548615</v>
       </c>
       <c r="B146" t="n">
         <v>78560</v>
@@ -15560,10 +15560,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>480319</v>
+        <v>480367</v>
       </c>
       <c r="R146" t="n">
-        <v>6826923</v>
+        <v>6826868</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15622,7 +15622,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119548615</v>
+        <v>119548619</v>
       </c>
       <c r="B147" t="n">
         <v>78560</v>
@@ -15662,10 +15662,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>480367</v>
+        <v>480413</v>
       </c>
       <c r="R147" t="n">
-        <v>6826868</v>
+        <v>6826839</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15724,10 +15724,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119548619</v>
+        <v>119548952</v>
       </c>
       <c r="B148" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15736,38 +15736,47 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>480413</v>
+        <v>480340</v>
       </c>
       <c r="R148" t="n">
-        <v>6826839</v>
+        <v>6826675</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15826,7 +15835,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119548952</v>
+        <v>119548967</v>
       </c>
       <c r="B149" t="n">
         <v>91840</v>
@@ -15859,26 +15868,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>480340</v>
+        <v>480322</v>
       </c>
       <c r="R149" t="n">
-        <v>6826675</v>
+        <v>6826949</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15937,10 +15937,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119548967</v>
+        <v>119548853</v>
       </c>
       <c r="B150" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15949,25 +15949,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15977,10 +15977,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>480322</v>
+        <v>480279</v>
       </c>
       <c r="R150" t="n">
-        <v>6826949</v>
+        <v>6826957</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16039,7 +16039,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119548853</v>
+        <v>119548905</v>
       </c>
       <c r="B151" t="n">
         <v>78526</v>
@@ -16079,10 +16079,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>480279</v>
+        <v>480469</v>
       </c>
       <c r="R151" t="n">
-        <v>6826957</v>
+        <v>6826655</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16141,7 +16141,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119548905</v>
+        <v>119548791</v>
       </c>
       <c r="B152" t="n">
         <v>78526</v>
@@ -16181,10 +16181,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>480469</v>
+        <v>480585</v>
       </c>
       <c r="R152" t="n">
-        <v>6826655</v>
+        <v>6826740</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16243,7 +16243,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119548791</v>
+        <v>119548838</v>
       </c>
       <c r="B153" t="n">
         <v>78526</v>
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>480585</v>
+        <v>480207</v>
       </c>
       <c r="R153" t="n">
-        <v>6826740</v>
+        <v>6827008</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16345,7 +16345,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119548838</v>
+        <v>119548835</v>
       </c>
       <c r="B154" t="n">
         <v>78526</v>
@@ -16385,10 +16385,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>480207</v>
+        <v>480162</v>
       </c>
       <c r="R154" t="n">
-        <v>6827008</v>
+        <v>6827015</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16447,7 +16447,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119548835</v>
+        <v>119548880</v>
       </c>
       <c r="B155" t="n">
         <v>78526</v>
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>480162</v>
+        <v>480375</v>
       </c>
       <c r="R155" t="n">
-        <v>6827015</v>
+        <v>6826874</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16549,7 +16549,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119548880</v>
+        <v>119548866</v>
       </c>
       <c r="B156" t="n">
         <v>78526</v>
@@ -16589,10 +16589,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>480375</v>
+        <v>480327</v>
       </c>
       <c r="R156" t="n">
-        <v>6826874</v>
+        <v>6826947</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16651,10 +16651,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119548866</v>
+        <v>119548996</v>
       </c>
       <c r="B157" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16667,21 +16667,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16691,10 +16691,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>480327</v>
+        <v>480115</v>
       </c>
       <c r="R157" t="n">
-        <v>6826947</v>
+        <v>6827003</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18802,10 +18802,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119548936</v>
+        <v>119548719</v>
       </c>
       <c r="B178" t="n">
-        <v>91840</v>
+        <v>90509</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18814,47 +18814,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4364</v>
+        <v>112</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>480462</v>
+        <v>480310</v>
       </c>
       <c r="R178" t="n">
-        <v>6826759</v>
+        <v>6826915</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18887,6 +18878,11 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>På kolad låga</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18913,10 +18909,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119548950</v>
+        <v>119549005</v>
       </c>
       <c r="B179" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18925,47 +18921,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>480102</v>
+        <v>480482</v>
       </c>
       <c r="R179" t="n">
-        <v>6826989</v>
+        <v>6826719</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19024,10 +19011,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119548961</v>
+        <v>119548614</v>
       </c>
       <c r="B180" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19036,25 +19023,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19064,10 +19051,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>480508</v>
+        <v>480370</v>
       </c>
       <c r="R180" t="n">
-        <v>6826508</v>
+        <v>6826871</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19126,10 +19113,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119548863</v>
+        <v>119548998</v>
       </c>
       <c r="B181" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19142,21 +19129,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19166,10 +19153,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>480333</v>
+        <v>480103</v>
       </c>
       <c r="R181" t="n">
-        <v>6826969</v>
+        <v>6827016</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19228,10 +19215,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119548893</v>
+        <v>119548624</v>
       </c>
       <c r="B182" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19244,21 +19231,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19268,10 +19255,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>480471</v>
+        <v>480486</v>
       </c>
       <c r="R182" t="n">
-        <v>6826805</v>
+        <v>6826811</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19330,10 +19317,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119548834</v>
+        <v>119549002</v>
       </c>
       <c r="B183" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19346,21 +19333,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19370,10 +19357,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>480182</v>
+        <v>480296</v>
       </c>
       <c r="R183" t="n">
-        <v>6827039</v>
+        <v>6826999</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19432,7 +19419,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119548953</v>
+        <v>119548936</v>
       </c>
       <c r="B184" t="n">
         <v>91840</v>
@@ -19467,7 +19454,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -19481,10 +19468,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>480476</v>
+        <v>480462</v>
       </c>
       <c r="R184" t="n">
-        <v>6826266</v>
+        <v>6826759</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19543,10 +19530,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119548701</v>
+        <v>119548950</v>
       </c>
       <c r="B185" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19555,38 +19542,47 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>480264</v>
+        <v>480102</v>
       </c>
       <c r="R185" t="n">
-        <v>6826923</v>
+        <v>6826989</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19645,10 +19641,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119548719</v>
+        <v>119548961</v>
       </c>
       <c r="B186" t="n">
-        <v>90509</v>
+        <v>91840</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19657,25 +19653,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19685,10 +19681,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>480310</v>
+        <v>480508</v>
       </c>
       <c r="R186" t="n">
-        <v>6826915</v>
+        <v>6826508</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19721,11 +19717,6 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>På kolad låga</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19752,10 +19743,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119549005</v>
+        <v>119548863</v>
       </c>
       <c r="B187" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19768,21 +19759,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19792,10 +19783,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>480482</v>
+        <v>480333</v>
       </c>
       <c r="R187" t="n">
-        <v>6826719</v>
+        <v>6826969</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19854,10 +19845,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119548614</v>
+        <v>119548893</v>
       </c>
       <c r="B188" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19870,21 +19861,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19894,10 +19885,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>480370</v>
+        <v>480471</v>
       </c>
       <c r="R188" t="n">
-        <v>6826871</v>
+        <v>6826805</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19956,10 +19947,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119548998</v>
+        <v>119548834</v>
       </c>
       <c r="B189" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19972,21 +19963,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19996,10 +19987,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>480103</v>
+        <v>480182</v>
       </c>
       <c r="R189" t="n">
-        <v>6827016</v>
+        <v>6827039</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20058,10 +20049,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119548624</v>
+        <v>119548953</v>
       </c>
       <c r="B190" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20070,38 +20061,47 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>480486</v>
+        <v>480476</v>
       </c>
       <c r="R190" t="n">
-        <v>6826811</v>
+        <v>6826266</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20160,10 +20160,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119549002</v>
+        <v>119548667</v>
       </c>
       <c r="B191" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20176,21 +20176,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20200,10 +20200,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>480296</v>
+        <v>480487</v>
       </c>
       <c r="R191" t="n">
-        <v>6826999</v>
+        <v>6826498</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20262,7 +20262,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119548667</v>
+        <v>119548672</v>
       </c>
       <c r="B192" t="n">
         <v>79144</v>
@@ -20302,10 +20302,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>480487</v>
+        <v>480476</v>
       </c>
       <c r="R192" t="n">
-        <v>6826498</v>
+        <v>6826268</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20364,10 +20364,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119548672</v>
+        <v>119548701</v>
       </c>
       <c r="B193" t="n">
-        <v>79144</v>
+        <v>57463</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20380,21 +20380,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20404,10 +20404,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>480476</v>
+        <v>480264</v>
       </c>
       <c r="R193" t="n">
-        <v>6826268</v>
+        <v>6826923</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20466,10 +20466,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119548795</v>
+        <v>119548757</v>
       </c>
       <c r="B194" t="n">
-        <v>78526</v>
+        <v>90712</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20478,25 +20478,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20506,10 +20506,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>480463</v>
+        <v>480315</v>
       </c>
       <c r="R194" t="n">
-        <v>6826780</v>
+        <v>6826838</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20568,10 +20568,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119548813</v>
+        <v>119548930</v>
       </c>
       <c r="B195" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20580,38 +20580,47 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>480175</v>
+        <v>480228</v>
       </c>
       <c r="R195" t="n">
-        <v>6826949</v>
+        <v>6827065</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20670,7 +20679,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119548908</v>
+        <v>119548795</v>
       </c>
       <c r="B196" t="n">
         <v>78526</v>
@@ -20710,10 +20719,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>480478</v>
+        <v>480463</v>
       </c>
       <c r="R196" t="n">
-        <v>6826636</v>
+        <v>6826780</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20772,7 +20781,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119548828</v>
+        <v>119548813</v>
       </c>
       <c r="B197" t="n">
         <v>78526</v>
@@ -20812,10 +20821,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>480217</v>
+        <v>480175</v>
       </c>
       <c r="R197" t="n">
-        <v>6827061</v>
+        <v>6826949</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20874,7 +20883,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119548849</v>
+        <v>119548908</v>
       </c>
       <c r="B198" t="n">
         <v>78526</v>
@@ -20914,10 +20923,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>480249</v>
+        <v>480478</v>
       </c>
       <c r="R198" t="n">
-        <v>6826948</v>
+        <v>6826636</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20976,7 +20985,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119548793</v>
+        <v>119548828</v>
       </c>
       <c r="B199" t="n">
         <v>78526</v>
@@ -21016,10 +21025,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>480514</v>
+        <v>480217</v>
       </c>
       <c r="R199" t="n">
-        <v>6826733</v>
+        <v>6827061</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21078,7 +21087,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119548879</v>
+        <v>119548849</v>
       </c>
       <c r="B200" t="n">
         <v>78526</v>
@@ -21118,10 +21127,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>480367</v>
+        <v>480249</v>
       </c>
       <c r="R200" t="n">
-        <v>6826875</v>
+        <v>6826948</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21180,7 +21189,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119548782</v>
+        <v>119548793</v>
       </c>
       <c r="B201" t="n">
         <v>78526</v>
@@ -21223,7 +21232,7 @@
         <v>480514</v>
       </c>
       <c r="R201" t="n">
-        <v>6826561</v>
+        <v>6826733</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21282,7 +21291,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119548809</v>
+        <v>119548879</v>
       </c>
       <c r="B202" t="n">
         <v>78526</v>
@@ -21322,10 +21331,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>480194</v>
+        <v>480367</v>
       </c>
       <c r="R202" t="n">
-        <v>6826929</v>
+        <v>6826875</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21384,7 +21393,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119548839</v>
+        <v>119548782</v>
       </c>
       <c r="B203" t="n">
         <v>78526</v>
@@ -21424,10 +21433,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>480230</v>
+        <v>480514</v>
       </c>
       <c r="R203" t="n">
-        <v>6827011</v>
+        <v>6826561</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21486,10 +21495,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119548757</v>
+        <v>119548809</v>
       </c>
       <c r="B204" t="n">
-        <v>90712</v>
+        <v>78526</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21498,25 +21507,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21526,10 +21535,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>480315</v>
+        <v>480194</v>
       </c>
       <c r="R204" t="n">
-        <v>6826838</v>
+        <v>6826929</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21588,10 +21597,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119548930</v>
+        <v>119548839</v>
       </c>
       <c r="B205" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21600,47 +21609,38 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>480228</v>
+        <v>480230</v>
       </c>
       <c r="R205" t="n">
-        <v>6827065</v>
+        <v>6827011</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -25278,10 +25278,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>119548888</v>
+        <v>119548668</v>
       </c>
       <c r="B241" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25294,21 +25294,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>480425</v>
+        <v>480500</v>
       </c>
       <c r="R241" t="n">
-        <v>6826841</v>
+        <v>6826452</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25380,10 +25380,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>119548668</v>
+        <v>119548888</v>
       </c>
       <c r="B242" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25396,21 +25396,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25420,10 +25420,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>480500</v>
+        <v>480425</v>
       </c>
       <c r="R242" t="n">
-        <v>6826452</v>
+        <v>6826841</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -26638,10 +26638,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>119582950</v>
+        <v>119582604</v>
       </c>
       <c r="B254" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26650,41 +26650,41 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>480695</v>
+        <v>480554</v>
       </c>
       <c r="R254" t="n">
-        <v>6826849</v>
+        <v>6826774</v>
       </c>
       <c r="S254" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -26711,9 +26711,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -26728,22 +26738,22 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>119582604</v>
+        <v>119582950</v>
       </c>
       <c r="B255" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26752,41 +26762,41 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>480554</v>
+        <v>480695</v>
       </c>
       <c r="R255" t="n">
-        <v>6826774</v>
+        <v>6826849</v>
       </c>
       <c r="S255" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -26813,19 +26823,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -26840,12 +26840,12 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
@@ -27513,10 +27513,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>119581581</v>
+        <v>119583019</v>
       </c>
       <c r="B262" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27525,25 +27525,25 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27553,10 +27553,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>480538</v>
+        <v>480716</v>
       </c>
       <c r="R262" t="n">
-        <v>6826770</v>
+        <v>6826851</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27615,10 +27615,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>119583227</v>
+        <v>119581581</v>
       </c>
       <c r="B263" t="n">
-        <v>78262</v>
+        <v>91884</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27631,37 +27631,37 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>480664</v>
+        <v>480538</v>
       </c>
       <c r="R263" t="n">
-        <v>6826993</v>
+        <v>6826770</v>
       </c>
       <c r="S263" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -27688,19 +27688,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -27715,22 +27705,22 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>119583019</v>
+        <v>119583227</v>
       </c>
       <c r="B264" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27739,41 +27729,41 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>480716</v>
+        <v>480664</v>
       </c>
       <c r="R264" t="n">
-        <v>6826851</v>
+        <v>6826993</v>
       </c>
       <c r="S264" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -27800,9 +27790,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -27817,12 +27817,12 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
@@ -29305,10 +29305,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>119579158</v>
+        <v>119583130</v>
       </c>
       <c r="B279" t="n">
-        <v>89633</v>
+        <v>79643</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -29317,38 +29317,38 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>1962</v>
+        <v>6464</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>480467</v>
+        <v>480684</v>
       </c>
       <c r="R279" t="n">
-        <v>6827000</v>
+        <v>6826961</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -29407,10 +29407,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>119583220</v>
+        <v>119579158</v>
       </c>
       <c r="B280" t="n">
-        <v>78526</v>
+        <v>89633</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -29423,34 +29423,34 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>480667</v>
+        <v>480467</v>
       </c>
       <c r="R280" t="n">
-        <v>6826982</v>
+        <v>6827000</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29509,7 +29509,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>119581465</v>
+        <v>119583220</v>
       </c>
       <c r="B281" t="n">
         <v>78526</v>
@@ -29549,10 +29549,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>480544</v>
+        <v>480667</v>
       </c>
       <c r="R281" t="n">
-        <v>6826825</v>
+        <v>6826982</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29611,7 +29611,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>119583661</v>
+        <v>119581465</v>
       </c>
       <c r="B282" t="n">
         <v>78526</v>
@@ -29647,17 +29647,17 @@
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>480558</v>
+        <v>480544</v>
       </c>
       <c r="R282" t="n">
-        <v>6827045</v>
+        <v>6826825</v>
       </c>
       <c r="S282" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -29684,24 +29684,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z282" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA282" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB282" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC282" t="inlineStr">
-        <is>
-          <t>På talstam</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -29716,22 +29701,22 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>119583130</v>
+        <v>119583661</v>
       </c>
       <c r="B283" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -29740,41 +29725,41 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>480684</v>
+        <v>480558</v>
       </c>
       <c r="R283" t="n">
-        <v>6826961</v>
+        <v>6827045</v>
       </c>
       <c r="S283" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -29801,9 +29786,24 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA283" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>På talstam</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -29818,12 +29818,12 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
@@ -31409,10 +31409,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>119582210</v>
+        <v>119582910</v>
       </c>
       <c r="B299" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -31421,47 +31421,38 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>480495</v>
+        <v>480778</v>
       </c>
       <c r="R299" t="n">
-        <v>6826796</v>
+        <v>6826820</v>
       </c>
       <c r="S299" t="n">
         <v>9</v>
@@ -31493,7 +31484,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -31503,7 +31494,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -31530,10 +31521,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>119582910</v>
+        <v>119582210</v>
       </c>
       <c r="B300" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -31542,38 +31533,47 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>480778</v>
+        <v>480495</v>
       </c>
       <c r="R300" t="n">
-        <v>6826820</v>
+        <v>6826796</v>
       </c>
       <c r="S300" t="n">
         <v>9</v>
@@ -31605,7 +31605,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -31615,7 +31615,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -34967,10 +34967,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>119672810</v>
+        <v>119672821</v>
       </c>
       <c r="B333" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -34979,25 +34979,25 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
@@ -35007,10 +35007,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>480583</v>
+        <v>480566</v>
       </c>
       <c r="R333" t="n">
-        <v>6826837</v>
+        <v>6826703</v>
       </c>
       <c r="S333" t="n">
         <v>1</v>
@@ -35069,7 +35069,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>119672821</v>
+        <v>119672820</v>
       </c>
       <c r="B334" t="n">
         <v>91840</v>
@@ -35109,10 +35109,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>480566</v>
+        <v>480670</v>
       </c>
       <c r="R334" t="n">
-        <v>6826703</v>
+        <v>6826723</v>
       </c>
       <c r="S334" t="n">
         <v>1</v>
@@ -35171,10 +35171,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>119672820</v>
+        <v>119672810</v>
       </c>
       <c r="B335" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -35183,25 +35183,25 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
@@ -35211,10 +35211,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>480670</v>
+        <v>480583</v>
       </c>
       <c r="R335" t="n">
-        <v>6826723</v>
+        <v>6826837</v>
       </c>
       <c r="S335" t="n">
         <v>1</v>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -2112,7 +2112,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119548935</v>
+        <v>119548944</v>
       </c>
       <c r="B16" t="n">
         <v>91840</v>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480185</v>
+        <v>480164</v>
       </c>
       <c r="R16" t="n">
-        <v>6827084</v>
+        <v>6827086</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119548929</v>
+        <v>119548988</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,47 +2235,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480234</v>
+        <v>480593</v>
       </c>
       <c r="R17" t="n">
-        <v>6827072</v>
+        <v>6826669</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2334,7 +2325,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119548966</v>
+        <v>119548935</v>
       </c>
       <c r="B18" t="n">
         <v>91840</v>
@@ -2367,17 +2358,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480124</v>
+        <v>480185</v>
       </c>
       <c r="R18" t="n">
-        <v>6826991</v>
+        <v>6827084</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119548892</v>
+        <v>119548929</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2448,38 +2448,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480462</v>
+        <v>480234</v>
       </c>
       <c r="R19" t="n">
-        <v>6826805</v>
+        <v>6827072</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2538,10 +2547,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119548882</v>
+        <v>119548966</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2550,25 +2559,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2578,10 +2587,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480360</v>
+        <v>480124</v>
       </c>
       <c r="R20" t="n">
-        <v>6826858</v>
+        <v>6826991</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2640,7 +2649,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119548860</v>
+        <v>119548892</v>
       </c>
       <c r="B21" t="n">
         <v>78526</v>
@@ -2680,10 +2689,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480325</v>
+        <v>480462</v>
       </c>
       <c r="R21" t="n">
-        <v>6826987</v>
+        <v>6826805</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,7 +2751,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119548830</v>
+        <v>119548882</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2782,10 +2791,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480214</v>
+        <v>480360</v>
       </c>
       <c r="R22" t="n">
-        <v>6827047</v>
+        <v>6826858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2844,7 +2853,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119548890</v>
+        <v>119548860</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -2884,10 +2893,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480454</v>
+        <v>480325</v>
       </c>
       <c r="R23" t="n">
-        <v>6826841</v>
+        <v>6826987</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2946,7 +2955,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119548825</v>
+        <v>119548830</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -2986,10 +2995,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480165</v>
+        <v>480214</v>
       </c>
       <c r="R24" t="n">
-        <v>6827078</v>
+        <v>6827047</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,10 +3057,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119548944</v>
+        <v>119548890</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3060,47 +3069,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480164</v>
+        <v>480454</v>
       </c>
       <c r="R25" t="n">
-        <v>6827086</v>
+        <v>6826841</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3159,10 +3159,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119548988</v>
+        <v>119548825</v>
       </c>
       <c r="B26" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3175,21 +3175,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480593</v>
+        <v>480165</v>
       </c>
       <c r="R26" t="n">
-        <v>6826669</v>
+        <v>6827078</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -13462,10 +13462,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119548607</v>
+        <v>119548832</v>
       </c>
       <c r="B126" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13478,21 +13478,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13502,10 +13502,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>480246</v>
+        <v>480199</v>
       </c>
       <c r="R126" t="n">
-        <v>6827003</v>
+        <v>6827042</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13564,7 +13564,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119548832</v>
+        <v>119548843</v>
       </c>
       <c r="B127" t="n">
         <v>78526</v>
@@ -13604,10 +13604,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>480199</v>
+        <v>480272</v>
       </c>
       <c r="R127" t="n">
-        <v>6827042</v>
+        <v>6826977</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13666,7 +13666,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119548843</v>
+        <v>119548814</v>
       </c>
       <c r="B128" t="n">
         <v>78526</v>
@@ -13706,10 +13706,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>480272</v>
+        <v>480167</v>
       </c>
       <c r="R128" t="n">
-        <v>6826977</v>
+        <v>6826957</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13768,7 +13768,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119548814</v>
+        <v>119548898</v>
       </c>
       <c r="B129" t="n">
         <v>78526</v>
@@ -13808,10 +13808,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>480167</v>
+        <v>480497</v>
       </c>
       <c r="R129" t="n">
-        <v>6826957</v>
+        <v>6826742</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13870,7 +13870,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119548898</v>
+        <v>119548824</v>
       </c>
       <c r="B130" t="n">
         <v>78526</v>
@@ -13910,10 +13910,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>480497</v>
+        <v>480160</v>
       </c>
       <c r="R130" t="n">
-        <v>6826742</v>
+        <v>6827090</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13972,7 +13972,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119548824</v>
+        <v>119548821</v>
       </c>
       <c r="B131" t="n">
         <v>78526</v>
@@ -14012,10 +14012,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>480160</v>
+        <v>480118</v>
       </c>
       <c r="R131" t="n">
-        <v>6827090</v>
+        <v>6827059</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119548821</v>
+        <v>119548784</v>
       </c>
       <c r="B132" t="n">
         <v>78526</v>
@@ -14114,10 +14114,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>480118</v>
+        <v>480530</v>
       </c>
       <c r="R132" t="n">
-        <v>6827059</v>
+        <v>6826604</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14176,10 +14176,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119548784</v>
+        <v>119548938</v>
       </c>
       <c r="B133" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14188,38 +14188,47 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>480530</v>
+        <v>480389</v>
       </c>
       <c r="R133" t="n">
-        <v>6826604</v>
+        <v>6826810</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14278,10 +14287,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119548938</v>
+        <v>119548607</v>
       </c>
       <c r="B134" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14290,47 +14299,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>480389</v>
+        <v>480246</v>
       </c>
       <c r="R134" t="n">
-        <v>6826810</v>
+        <v>6827003</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15418,10 +15418,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119548604</v>
+        <v>119548996</v>
       </c>
       <c r="B145" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15434,21 +15434,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15458,10 +15458,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>480319</v>
+        <v>480115</v>
       </c>
       <c r="R145" t="n">
-        <v>6826923</v>
+        <v>6827003</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15520,7 +15520,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119548615</v>
+        <v>119548604</v>
       </c>
       <c r="B146" t="n">
         <v>78560</v>
@@ -15560,10 +15560,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>480367</v>
+        <v>480319</v>
       </c>
       <c r="R146" t="n">
-        <v>6826868</v>
+        <v>6826923</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15622,7 +15622,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119548619</v>
+        <v>119548615</v>
       </c>
       <c r="B147" t="n">
         <v>78560</v>
@@ -15662,10 +15662,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>480413</v>
+        <v>480367</v>
       </c>
       <c r="R147" t="n">
-        <v>6826839</v>
+        <v>6826868</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15724,10 +15724,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119548952</v>
+        <v>119548619</v>
       </c>
       <c r="B148" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15736,47 +15736,38 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>480340</v>
+        <v>480413</v>
       </c>
       <c r="R148" t="n">
-        <v>6826675</v>
+        <v>6826839</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15835,7 +15826,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119548967</v>
+        <v>119548952</v>
       </c>
       <c r="B149" t="n">
         <v>91840</v>
@@ -15868,17 +15859,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>480322</v>
+        <v>480340</v>
       </c>
       <c r="R149" t="n">
-        <v>6826949</v>
+        <v>6826675</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15937,10 +15937,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119548853</v>
+        <v>119548967</v>
       </c>
       <c r="B150" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15949,25 +15949,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15977,10 +15977,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>480279</v>
+        <v>480322</v>
       </c>
       <c r="R150" t="n">
-        <v>6826957</v>
+        <v>6826949</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16039,7 +16039,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119548905</v>
+        <v>119548853</v>
       </c>
       <c r="B151" t="n">
         <v>78526</v>
@@ -16079,10 +16079,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>480469</v>
+        <v>480279</v>
       </c>
       <c r="R151" t="n">
-        <v>6826655</v>
+        <v>6826957</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16141,7 +16141,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119548791</v>
+        <v>119548905</v>
       </c>
       <c r="B152" t="n">
         <v>78526</v>
@@ -16181,10 +16181,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>480585</v>
+        <v>480469</v>
       </c>
       <c r="R152" t="n">
-        <v>6826740</v>
+        <v>6826655</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16243,7 +16243,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119548838</v>
+        <v>119548791</v>
       </c>
       <c r="B153" t="n">
         <v>78526</v>
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>480207</v>
+        <v>480585</v>
       </c>
       <c r="R153" t="n">
-        <v>6827008</v>
+        <v>6826740</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16345,7 +16345,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119548835</v>
+        <v>119548838</v>
       </c>
       <c r="B154" t="n">
         <v>78526</v>
@@ -16385,10 +16385,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>480162</v>
+        <v>480207</v>
       </c>
       <c r="R154" t="n">
-        <v>6827015</v>
+        <v>6827008</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16447,7 +16447,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119548880</v>
+        <v>119548835</v>
       </c>
       <c r="B155" t="n">
         <v>78526</v>
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>480375</v>
+        <v>480162</v>
       </c>
       <c r="R155" t="n">
-        <v>6826874</v>
+        <v>6827015</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16549,7 +16549,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119548866</v>
+        <v>119548880</v>
       </c>
       <c r="B156" t="n">
         <v>78526</v>
@@ -16589,10 +16589,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>480327</v>
+        <v>480375</v>
       </c>
       <c r="R156" t="n">
-        <v>6826947</v>
+        <v>6826874</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16651,10 +16651,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119548996</v>
+        <v>119548866</v>
       </c>
       <c r="B157" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16667,21 +16667,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16691,10 +16691,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>480115</v>
+        <v>480327</v>
       </c>
       <c r="R157" t="n">
-        <v>6827003</v>
+        <v>6826947</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18802,10 +18802,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119548719</v>
+        <v>119548936</v>
       </c>
       <c r="B178" t="n">
-        <v>90509</v>
+        <v>91840</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18814,38 +18814,47 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>480310</v>
+        <v>480462</v>
       </c>
       <c r="R178" t="n">
-        <v>6826915</v>
+        <v>6826759</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18878,11 +18887,6 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>På kolad låga</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18909,10 +18913,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119549005</v>
+        <v>119548950</v>
       </c>
       <c r="B179" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18921,38 +18925,47 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>480482</v>
+        <v>480102</v>
       </c>
       <c r="R179" t="n">
-        <v>6826719</v>
+        <v>6826989</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19011,10 +19024,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119548614</v>
+        <v>119548961</v>
       </c>
       <c r="B180" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19023,25 +19036,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19051,10 +19064,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>480370</v>
+        <v>480508</v>
       </c>
       <c r="R180" t="n">
-        <v>6826871</v>
+        <v>6826508</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19113,10 +19126,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119548998</v>
+        <v>119548863</v>
       </c>
       <c r="B181" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19129,21 +19142,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19153,10 +19166,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>480103</v>
+        <v>480333</v>
       </c>
       <c r="R181" t="n">
-        <v>6827016</v>
+        <v>6826969</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19215,10 +19228,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119548624</v>
+        <v>119548893</v>
       </c>
       <c r="B182" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19231,21 +19244,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19255,10 +19268,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>480486</v>
+        <v>480471</v>
       </c>
       <c r="R182" t="n">
-        <v>6826811</v>
+        <v>6826805</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19317,10 +19330,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119549002</v>
+        <v>119548834</v>
       </c>
       <c r="B183" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19333,21 +19346,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19357,10 +19370,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>480296</v>
+        <v>480182</v>
       </c>
       <c r="R183" t="n">
-        <v>6826999</v>
+        <v>6827039</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19419,7 +19432,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119548936</v>
+        <v>119548953</v>
       </c>
       <c r="B184" t="n">
         <v>91840</v>
@@ -19454,7 +19467,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -19468,10 +19481,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>480462</v>
+        <v>480476</v>
       </c>
       <c r="R184" t="n">
-        <v>6826759</v>
+        <v>6826266</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19530,10 +19543,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119548950</v>
+        <v>119548701</v>
       </c>
       <c r="B185" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19542,47 +19555,38 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>480102</v>
+        <v>480264</v>
       </c>
       <c r="R185" t="n">
-        <v>6826989</v>
+        <v>6826923</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19641,10 +19645,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119548961</v>
+        <v>119548719</v>
       </c>
       <c r="B186" t="n">
-        <v>91840</v>
+        <v>90509</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19653,25 +19657,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4364</v>
+        <v>112</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19681,10 +19685,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>480508</v>
+        <v>480310</v>
       </c>
       <c r="R186" t="n">
-        <v>6826508</v>
+        <v>6826915</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19717,6 +19721,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>På kolad låga</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19743,10 +19752,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119548863</v>
+        <v>119549005</v>
       </c>
       <c r="B187" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19759,21 +19768,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19783,10 +19792,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>480333</v>
+        <v>480482</v>
       </c>
       <c r="R187" t="n">
-        <v>6826969</v>
+        <v>6826719</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19845,10 +19854,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119548893</v>
+        <v>119548614</v>
       </c>
       <c r="B188" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19861,21 +19870,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19885,10 +19894,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>480471</v>
+        <v>480370</v>
       </c>
       <c r="R188" t="n">
-        <v>6826805</v>
+        <v>6826871</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19947,10 +19956,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119548834</v>
+        <v>119548998</v>
       </c>
       <c r="B189" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19963,21 +19972,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19987,10 +19996,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>480182</v>
+        <v>480103</v>
       </c>
       <c r="R189" t="n">
-        <v>6827039</v>
+        <v>6827016</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20049,10 +20058,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119548953</v>
+        <v>119548624</v>
       </c>
       <c r="B190" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20061,47 +20070,38 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>480476</v>
+        <v>480486</v>
       </c>
       <c r="R190" t="n">
-        <v>6826266</v>
+        <v>6826811</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20160,10 +20160,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119548667</v>
+        <v>119549002</v>
       </c>
       <c r="B191" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20176,21 +20176,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20200,10 +20200,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>480487</v>
+        <v>480296</v>
       </c>
       <c r="R191" t="n">
-        <v>6826498</v>
+        <v>6826999</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20262,7 +20262,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119548672</v>
+        <v>119548667</v>
       </c>
       <c r="B192" t="n">
         <v>79144</v>
@@ -20302,10 +20302,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>480476</v>
+        <v>480487</v>
       </c>
       <c r="R192" t="n">
-        <v>6826268</v>
+        <v>6826498</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20364,10 +20364,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119548701</v>
+        <v>119548672</v>
       </c>
       <c r="B193" t="n">
-        <v>57463</v>
+        <v>79144</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20380,21 +20380,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20404,10 +20404,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>480264</v>
+        <v>480476</v>
       </c>
       <c r="R193" t="n">
-        <v>6826923</v>
+        <v>6826268</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20466,10 +20466,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119548757</v>
+        <v>119548795</v>
       </c>
       <c r="B194" t="n">
-        <v>90712</v>
+        <v>78526</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20478,25 +20478,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20506,10 +20506,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>480315</v>
+        <v>480463</v>
       </c>
       <c r="R194" t="n">
-        <v>6826838</v>
+        <v>6826780</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20568,10 +20568,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119548930</v>
+        <v>119548813</v>
       </c>
       <c r="B195" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20580,47 +20580,38 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>480228</v>
+        <v>480175</v>
       </c>
       <c r="R195" t="n">
-        <v>6827065</v>
+        <v>6826949</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20679,7 +20670,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119548795</v>
+        <v>119548908</v>
       </c>
       <c r="B196" t="n">
         <v>78526</v>
@@ -20719,10 +20710,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>480463</v>
+        <v>480478</v>
       </c>
       <c r="R196" t="n">
-        <v>6826780</v>
+        <v>6826636</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20781,7 +20772,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119548813</v>
+        <v>119548828</v>
       </c>
       <c r="B197" t="n">
         <v>78526</v>
@@ -20821,10 +20812,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>480175</v>
+        <v>480217</v>
       </c>
       <c r="R197" t="n">
-        <v>6826949</v>
+        <v>6827061</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20883,7 +20874,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119548908</v>
+        <v>119548849</v>
       </c>
       <c r="B198" t="n">
         <v>78526</v>
@@ -20923,10 +20914,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>480478</v>
+        <v>480249</v>
       </c>
       <c r="R198" t="n">
-        <v>6826636</v>
+        <v>6826948</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20985,7 +20976,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119548828</v>
+        <v>119548793</v>
       </c>
       <c r="B199" t="n">
         <v>78526</v>
@@ -21025,10 +21016,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>480217</v>
+        <v>480514</v>
       </c>
       <c r="R199" t="n">
-        <v>6827061</v>
+        <v>6826733</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21087,7 +21078,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119548849</v>
+        <v>119548879</v>
       </c>
       <c r="B200" t="n">
         <v>78526</v>
@@ -21127,10 +21118,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>480249</v>
+        <v>480367</v>
       </c>
       <c r="R200" t="n">
-        <v>6826948</v>
+        <v>6826875</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21189,7 +21180,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119548793</v>
+        <v>119548782</v>
       </c>
       <c r="B201" t="n">
         <v>78526</v>
@@ -21232,7 +21223,7 @@
         <v>480514</v>
       </c>
       <c r="R201" t="n">
-        <v>6826733</v>
+        <v>6826561</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21291,7 +21282,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119548879</v>
+        <v>119548809</v>
       </c>
       <c r="B202" t="n">
         <v>78526</v>
@@ -21331,10 +21322,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>480367</v>
+        <v>480194</v>
       </c>
       <c r="R202" t="n">
-        <v>6826875</v>
+        <v>6826929</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21393,7 +21384,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119548782</v>
+        <v>119548839</v>
       </c>
       <c r="B203" t="n">
         <v>78526</v>
@@ -21433,10 +21424,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>480514</v>
+        <v>480230</v>
       </c>
       <c r="R203" t="n">
-        <v>6826561</v>
+        <v>6827011</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21495,10 +21486,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119548809</v>
+        <v>119548757</v>
       </c>
       <c r="B204" t="n">
-        <v>78526</v>
+        <v>90712</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21507,25 +21498,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21535,10 +21526,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>480194</v>
+        <v>480315</v>
       </c>
       <c r="R204" t="n">
-        <v>6826929</v>
+        <v>6826838</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21597,10 +21588,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119548839</v>
+        <v>119548930</v>
       </c>
       <c r="B205" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21609,38 +21600,47 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>480230</v>
+        <v>480228</v>
       </c>
       <c r="R205" t="n">
-        <v>6827011</v>
+        <v>6827065</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21903,7 +21903,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119548817</v>
+        <v>119548812</v>
       </c>
       <c r="B208" t="n">
         <v>78526</v>
@@ -21943,10 +21943,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>480145</v>
+        <v>480181</v>
       </c>
       <c r="R208" t="n">
-        <v>6826961</v>
+        <v>6826939</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22005,7 +22005,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119548799</v>
+        <v>119548895</v>
       </c>
       <c r="B209" t="n">
         <v>78526</v>
@@ -22045,10 +22045,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>480325</v>
+        <v>480486</v>
       </c>
       <c r="R209" t="n">
-        <v>6826837</v>
+        <v>6826811</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22107,10 +22107,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119548812</v>
+        <v>119548665</v>
       </c>
       <c r="B210" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22123,21 +22123,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22147,10 +22147,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>480181</v>
+        <v>480477</v>
       </c>
       <c r="R210" t="n">
-        <v>6826939</v>
+        <v>6826655</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22209,10 +22209,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119548895</v>
+        <v>119548671</v>
       </c>
       <c r="B211" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22225,21 +22225,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22249,10 +22249,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>480486</v>
+        <v>480469</v>
       </c>
       <c r="R211" t="n">
-        <v>6826811</v>
+        <v>6826386</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22311,10 +22311,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119548665</v>
+        <v>119549011</v>
       </c>
       <c r="B212" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22327,21 +22327,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22351,10 +22351,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>480477</v>
+        <v>480353</v>
       </c>
       <c r="R212" t="n">
-        <v>6826655</v>
+        <v>6826666</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22413,10 +22413,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119548671</v>
+        <v>119548995</v>
       </c>
       <c r="B213" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22429,21 +22429,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22453,10 +22453,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>480469</v>
+        <v>480105</v>
       </c>
       <c r="R213" t="n">
-        <v>6826386</v>
+        <v>6827006</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22515,10 +22515,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119548698</v>
+        <v>119548601</v>
       </c>
       <c r="B214" t="n">
-        <v>56522</v>
+        <v>78560</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22527,25 +22527,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22555,10 +22555,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>480248</v>
+        <v>480505</v>
       </c>
       <c r="R214" t="n">
-        <v>6826999</v>
+        <v>6826734</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22617,10 +22617,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119549011</v>
+        <v>119548621</v>
       </c>
       <c r="B215" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22633,21 +22633,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22657,10 +22657,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>480353</v>
+        <v>480425</v>
       </c>
       <c r="R215" t="n">
-        <v>6826666</v>
+        <v>6826841</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22719,10 +22719,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119548995</v>
+        <v>119548817</v>
       </c>
       <c r="B216" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22735,21 +22735,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22759,10 +22759,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>480105</v>
+        <v>480145</v>
       </c>
       <c r="R216" t="n">
-        <v>6827006</v>
+        <v>6826961</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22821,10 +22821,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119548601</v>
+        <v>119548799</v>
       </c>
       <c r="B217" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22837,21 +22837,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22861,10 +22861,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>480505</v>
+        <v>480325</v>
       </c>
       <c r="R217" t="n">
-        <v>6826734</v>
+        <v>6826837</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22923,10 +22923,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119548621</v>
+        <v>119548698</v>
       </c>
       <c r="B218" t="n">
-        <v>78560</v>
+        <v>56522</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22935,25 +22935,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22963,10 +22963,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>480425</v>
+        <v>480248</v>
       </c>
       <c r="R218" t="n">
-        <v>6826841</v>
+        <v>6826999</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -28140,10 +28140,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>119582533</v>
+        <v>119580401</v>
       </c>
       <c r="B268" t="n">
-        <v>78560</v>
+        <v>79115</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28156,34 +28156,34 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>480732</v>
+        <v>480542</v>
       </c>
       <c r="R268" t="n">
-        <v>6826736</v>
+        <v>6827033</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28349,10 +28349,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>119580401</v>
+        <v>119582533</v>
       </c>
       <c r="B270" t="n">
-        <v>79115</v>
+        <v>78560</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28365,34 +28365,34 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>480542</v>
+        <v>480732</v>
       </c>
       <c r="R270" t="n">
-        <v>6827033</v>
+        <v>6826736</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -2733,10 +2733,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119548704</v>
+        <v>119548616</v>
       </c>
       <c r="B22" t="n">
-        <v>57463</v>
+        <v>78560</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2749,21 +2749,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480161</v>
+        <v>480361</v>
       </c>
       <c r="R22" t="n">
-        <v>6827018</v>
+        <v>6826860</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119548616</v>
+        <v>119548990</v>
       </c>
       <c r="B23" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480361</v>
+        <v>480454</v>
       </c>
       <c r="R23" t="n">
-        <v>6826860</v>
+        <v>6826787</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119548716</v>
+        <v>119548717</v>
       </c>
       <c r="B24" t="n">
         <v>91884</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480133</v>
+        <v>480157</v>
       </c>
       <c r="R24" t="n">
-        <v>6827087</v>
+        <v>6827091</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119548717</v>
+        <v>119548874</v>
       </c>
       <c r="B25" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3055,21 +3055,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480157</v>
+        <v>480359</v>
       </c>
       <c r="R25" t="n">
-        <v>6827091</v>
+        <v>6826914</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,10 +3141,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119548926</v>
+        <v>119548965</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3153,25 +3153,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480486</v>
+        <v>480116</v>
       </c>
       <c r="R26" t="n">
-        <v>6826356</v>
+        <v>6826996</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3243,10 +3243,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119548990</v>
+        <v>119548969</v>
       </c>
       <c r="B27" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3255,25 +3255,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480454</v>
+        <v>480390</v>
       </c>
       <c r="R27" t="n">
-        <v>6826787</v>
+        <v>6826677</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3345,10 +3345,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119548874</v>
+        <v>119548950</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3357,38 +3357,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480359</v>
+        <v>480102</v>
       </c>
       <c r="R28" t="n">
-        <v>6826914</v>
+        <v>6826989</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3447,10 +3456,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119548965</v>
+        <v>119548716</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3459,25 +3468,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3487,10 +3496,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480116</v>
+        <v>480133</v>
       </c>
       <c r="R29" t="n">
-        <v>6826996</v>
+        <v>6827087</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3549,10 +3558,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119548969</v>
+        <v>119548926</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3561,25 +3570,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,10 +3598,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480390</v>
+        <v>480486</v>
       </c>
       <c r="R30" t="n">
-        <v>6826677</v>
+        <v>6826356</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3651,10 +3660,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119548950</v>
+        <v>119548704</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3663,47 +3672,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480102</v>
+        <v>480161</v>
       </c>
       <c r="R31" t="n">
-        <v>6826989</v>
+        <v>6827018</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119548627</v>
+        <v>119548795</v>
       </c>
       <c r="B32" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3778,21 +3778,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480467</v>
+        <v>480463</v>
       </c>
       <c r="R32" t="n">
-        <v>6826666</v>
+        <v>6826780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119548719</v>
+        <v>119548876</v>
       </c>
       <c r="B33" t="n">
-        <v>90509</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480310</v>
+        <v>480383</v>
       </c>
       <c r="R33" t="n">
-        <v>6826915</v>
+        <v>6826888</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,11 +3940,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På kolad låga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3971,10 +3966,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119548626</v>
+        <v>119548904</v>
       </c>
       <c r="B34" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3987,21 +3982,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4011,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480437</v>
+        <v>480473</v>
       </c>
       <c r="R34" t="n">
-        <v>6826702</v>
+        <v>6826658</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4073,10 +4068,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119548904</v>
+        <v>119548968</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4085,25 +4080,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4113,10 +4108,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480473</v>
+        <v>480489</v>
       </c>
       <c r="R35" t="n">
-        <v>6826658</v>
+        <v>6826808</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4175,10 +4170,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119549005</v>
+        <v>119548627</v>
       </c>
       <c r="B36" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4191,21 +4186,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4215,10 +4210,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480482</v>
+        <v>480467</v>
       </c>
       <c r="R36" t="n">
-        <v>6826719</v>
+        <v>6826666</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4277,10 +4272,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119548795</v>
+        <v>119548719</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>90509</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4293,21 +4288,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4317,10 +4312,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480463</v>
+        <v>480310</v>
       </c>
       <c r="R37" t="n">
-        <v>6826780</v>
+        <v>6826915</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4353,6 +4348,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På kolad låga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4379,10 +4379,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119548876</v>
+        <v>119548626</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4395,21 +4395,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480383</v>
+        <v>480437</v>
       </c>
       <c r="R38" t="n">
-        <v>6826888</v>
+        <v>6826702</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119548968</v>
+        <v>119549005</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4493,25 +4493,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480489</v>
+        <v>480482</v>
       </c>
       <c r="R39" t="n">
-        <v>6826808</v>
+        <v>6826719</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4889,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119548807</v>
+        <v>119549004</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4905,21 +4905,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480283</v>
+        <v>480491</v>
       </c>
       <c r="R43" t="n">
-        <v>6826928</v>
+        <v>6826811</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4991,10 +4991,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119548783</v>
+        <v>119549012</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5007,21 +5007,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480513</v>
+        <v>480498</v>
       </c>
       <c r="R44" t="n">
-        <v>6826594</v>
+        <v>6826452</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5093,7 +5093,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119548862</v>
+        <v>119548807</v>
       </c>
       <c r="B45" t="n">
         <v>78526</v>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480325</v>
+        <v>480283</v>
       </c>
       <c r="R45" t="n">
-        <v>6826980</v>
+        <v>6826928</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119549004</v>
+        <v>119548783</v>
       </c>
       <c r="B46" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480491</v>
+        <v>480513</v>
       </c>
       <c r="R46" t="n">
-        <v>6826811</v>
+        <v>6826594</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119549012</v>
+        <v>119548862</v>
       </c>
       <c r="B47" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5313,21 +5313,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480498</v>
+        <v>480325</v>
       </c>
       <c r="R47" t="n">
-        <v>6826452</v>
+        <v>6826980</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5705,10 +5705,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119548623</v>
+        <v>119548753</v>
       </c>
       <c r="B51" t="n">
-        <v>78560</v>
+        <v>56514</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480462</v>
+        <v>480315</v>
       </c>
       <c r="R51" t="n">
-        <v>6826805</v>
+        <v>6826836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5807,7 +5807,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119548618</v>
+        <v>119548623</v>
       </c>
       <c r="B52" t="n">
         <v>78560</v>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480411</v>
+        <v>480462</v>
       </c>
       <c r="R52" t="n">
-        <v>6826833</v>
+        <v>6826805</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5909,10 +5909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119548756</v>
+        <v>119548618</v>
       </c>
       <c r="B53" t="n">
-        <v>90576</v>
+        <v>78560</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5925,21 +5925,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480208</v>
+        <v>480411</v>
       </c>
       <c r="R53" t="n">
-        <v>6826918</v>
+        <v>6826833</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6011,10 +6011,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119548653</v>
+        <v>119548734</v>
       </c>
       <c r="B54" t="n">
-        <v>79144</v>
+        <v>91863</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6027,21 +6027,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6051,10 +6051,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480489</v>
+        <v>480382</v>
       </c>
       <c r="R54" t="n">
-        <v>6826496</v>
+        <v>6826668</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119548662</v>
+        <v>119548832</v>
       </c>
       <c r="B55" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6129,21 +6129,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480419</v>
+        <v>480199</v>
       </c>
       <c r="R55" t="n">
-        <v>6826721</v>
+        <v>6827042</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6215,10 +6215,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119548947</v>
+        <v>119548653</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6227,47 +6227,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480500</v>
+        <v>480489</v>
       </c>
       <c r="R56" t="n">
-        <v>6826464</v>
+        <v>6826496</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,10 +6317,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119548966</v>
+        <v>119548662</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6338,25 +6329,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6366,10 +6357,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480124</v>
+        <v>480419</v>
       </c>
       <c r="R57" t="n">
-        <v>6826991</v>
+        <v>6826721</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6428,10 +6419,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119548998</v>
+        <v>119548947</v>
       </c>
       <c r="B58" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6440,38 +6431,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480103</v>
+        <v>480500</v>
       </c>
       <c r="R58" t="n">
-        <v>6827016</v>
+        <v>6826464</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119548813</v>
+        <v>119548966</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6542,25 +6542,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480175</v>
+        <v>480124</v>
       </c>
       <c r="R59" t="n">
-        <v>6826949</v>
+        <v>6826991</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6632,10 +6632,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119548858</v>
+        <v>119548698</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6644,25 +6644,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480300</v>
+        <v>480248</v>
       </c>
       <c r="R60" t="n">
         <v>6826999</v>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119548784</v>
+        <v>119548756</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6750,21 +6750,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480530</v>
+        <v>480208</v>
       </c>
       <c r="R61" t="n">
-        <v>6826604</v>
+        <v>6826918</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6836,10 +6836,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119548734</v>
+        <v>119548813</v>
       </c>
       <c r="B62" t="n">
-        <v>91863</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6852,21 +6852,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480382</v>
+        <v>480175</v>
       </c>
       <c r="R62" t="n">
-        <v>6826668</v>
+        <v>6826949</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6938,7 +6938,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119548832</v>
+        <v>119548858</v>
       </c>
       <c r="B63" t="n">
         <v>78526</v>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480199</v>
+        <v>480300</v>
       </c>
       <c r="R63" t="n">
-        <v>6827042</v>
+        <v>6826999</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119548753</v>
+        <v>119548784</v>
       </c>
       <c r="B64" t="n">
-        <v>56514</v>
+        <v>78526</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7056,21 +7056,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480315</v>
+        <v>480530</v>
       </c>
       <c r="R64" t="n">
-        <v>6826836</v>
+        <v>6826604</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7142,10 +7142,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119548698</v>
+        <v>119548998</v>
       </c>
       <c r="B65" t="n">
-        <v>56522</v>
+        <v>78171</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7154,25 +7154,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480248</v>
+        <v>480103</v>
       </c>
       <c r="R65" t="n">
-        <v>6826999</v>
+        <v>6827016</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8366,10 +8366,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119548942</v>
+        <v>119548625</v>
       </c>
       <c r="B77" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8378,47 +8378,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480378</v>
+        <v>480496</v>
       </c>
       <c r="R77" t="n">
-        <v>6826669</v>
+        <v>6826771</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8477,10 +8468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119548625</v>
+        <v>119548906</v>
       </c>
       <c r="B78" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8493,21 +8484,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8517,10 +8508,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480496</v>
+        <v>480466</v>
       </c>
       <c r="R78" t="n">
-        <v>6826771</v>
+        <v>6826649</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8579,7 +8570,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119548906</v>
+        <v>119548856</v>
       </c>
       <c r="B79" t="n">
         <v>78526</v>
@@ -8619,10 +8610,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480466</v>
+        <v>480296</v>
       </c>
       <c r="R79" t="n">
-        <v>6826649</v>
+        <v>6826982</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8681,7 +8672,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119548856</v>
+        <v>119548903</v>
       </c>
       <c r="B80" t="n">
         <v>78526</v>
@@ -8721,10 +8712,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480296</v>
+        <v>480468</v>
       </c>
       <c r="R80" t="n">
-        <v>6826982</v>
+        <v>6826667</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8783,10 +8774,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119548903</v>
+        <v>119548942</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8795,38 +8786,47 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480468</v>
+        <v>480378</v>
       </c>
       <c r="R81" t="n">
-        <v>6826667</v>
+        <v>6826669</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119548898</v>
+        <v>119548611</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9105,21 +9105,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480497</v>
+        <v>480297</v>
       </c>
       <c r="R84" t="n">
-        <v>6826742</v>
+        <v>6826966</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9191,10 +9191,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119548816</v>
+        <v>119549036</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9207,21 +9207,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9231,10 +9231,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480158</v>
+        <v>480107</v>
       </c>
       <c r="R85" t="n">
-        <v>6826964</v>
+        <v>6827011</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9293,10 +9293,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119548878</v>
+        <v>119548936</v>
       </c>
       <c r="B86" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9305,38 +9305,47 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>480370</v>
+        <v>480462</v>
       </c>
       <c r="R86" t="n">
-        <v>6826883</v>
+        <v>6826759</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9395,10 +9404,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119548811</v>
+        <v>119548934</v>
       </c>
       <c r="B87" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9407,38 +9416,47 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>480183</v>
+        <v>480127</v>
       </c>
       <c r="R87" t="n">
-        <v>6826936</v>
+        <v>6826954</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9497,10 +9515,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119548896</v>
+        <v>119548707</v>
       </c>
       <c r="B88" t="n">
-        <v>78526</v>
+        <v>91463</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9513,21 +9531,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9537,10 +9555,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>480491</v>
+        <v>480141</v>
       </c>
       <c r="R88" t="n">
-        <v>6826791</v>
+        <v>6826950</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9701,10 +9719,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119548611</v>
+        <v>119548991</v>
       </c>
       <c r="B90" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9717,21 +9735,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9741,10 +9759,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>480297</v>
+        <v>480337</v>
       </c>
       <c r="R90" t="n">
-        <v>6826966</v>
+        <v>6826835</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9803,10 +9821,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119549036</v>
+        <v>119548898</v>
       </c>
       <c r="B91" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9819,21 +9837,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9843,10 +9861,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>480107</v>
+        <v>480497</v>
       </c>
       <c r="R91" t="n">
-        <v>6827011</v>
+        <v>6826742</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9905,10 +9923,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119548707</v>
+        <v>119548816</v>
       </c>
       <c r="B92" t="n">
-        <v>91463</v>
+        <v>78526</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9921,21 +9939,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9945,10 +9963,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>480141</v>
+        <v>480158</v>
       </c>
       <c r="R92" t="n">
-        <v>6826950</v>
+        <v>6826964</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10007,10 +10025,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119548991</v>
+        <v>119548878</v>
       </c>
       <c r="B93" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10023,21 +10041,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10047,10 +10065,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>480337</v>
+        <v>480370</v>
       </c>
       <c r="R93" t="n">
-        <v>6826835</v>
+        <v>6826883</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10109,7 +10127,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119548863</v>
+        <v>119548811</v>
       </c>
       <c r="B94" t="n">
         <v>78526</v>
@@ -10149,10 +10167,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>480333</v>
+        <v>480183</v>
       </c>
       <c r="R94" t="n">
-        <v>6826969</v>
+        <v>6826936</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10211,10 +10229,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119548936</v>
+        <v>119548896</v>
       </c>
       <c r="B95" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10223,47 +10241,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>480462</v>
+        <v>480491</v>
       </c>
       <c r="R95" t="n">
-        <v>6826759</v>
+        <v>6826791</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10322,10 +10331,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119548934</v>
+        <v>119548863</v>
       </c>
       <c r="B96" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10334,47 +10343,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>480127</v>
+        <v>480333</v>
       </c>
       <c r="R96" t="n">
-        <v>6826954</v>
+        <v>6826969</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11462,10 +11462,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119548701</v>
+        <v>119549014</v>
       </c>
       <c r="B107" t="n">
-        <v>57463</v>
+        <v>78171</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11478,21 +11478,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11502,10 +11502,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>480264</v>
+        <v>480469</v>
       </c>
       <c r="R107" t="n">
-        <v>6826923</v>
+        <v>6826386</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11564,7 +11564,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119548700</v>
+        <v>119548701</v>
       </c>
       <c r="B108" t="n">
         <v>57463</v>
@@ -11597,21 +11597,17 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>480482</v>
+        <v>480264</v>
       </c>
       <c r="R108" t="n">
-        <v>6826326</v>
+        <v>6826923</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11670,10 +11666,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119548604</v>
+        <v>119548700</v>
       </c>
       <c r="B109" t="n">
-        <v>78560</v>
+        <v>57463</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11686,34 +11682,38 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>480319</v>
+        <v>480482</v>
       </c>
       <c r="R109" t="n">
-        <v>6826923</v>
+        <v>6826326</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11772,10 +11772,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119548631</v>
+        <v>119549009</v>
       </c>
       <c r="B110" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11788,21 +11788,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>480482</v>
+        <v>480362</v>
       </c>
       <c r="R110" t="n">
-        <v>6826629</v>
+        <v>6826679</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11874,10 +11874,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119548992</v>
+        <v>119548964</v>
       </c>
       <c r="B111" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11886,25 +11886,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11914,10 +11914,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>480293</v>
+        <v>480219</v>
       </c>
       <c r="R111" t="n">
-        <v>6826928</v>
+        <v>6826902</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11976,10 +11976,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119549014</v>
+        <v>119548954</v>
       </c>
       <c r="B112" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11988,38 +11988,47 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>480469</v>
+        <v>480107</v>
       </c>
       <c r="R112" t="n">
-        <v>6826386</v>
+        <v>6826990</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12078,10 +12087,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119549009</v>
+        <v>119548897</v>
       </c>
       <c r="B113" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12094,21 +12103,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12118,10 +12127,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>480362</v>
+        <v>480504</v>
       </c>
       <c r="R113" t="n">
-        <v>6826679</v>
+        <v>6826757</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12180,7 +12189,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119548802</v>
+        <v>119548879</v>
       </c>
       <c r="B114" t="n">
         <v>78526</v>
@@ -12220,10 +12229,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>480332</v>
+        <v>480367</v>
       </c>
       <c r="R114" t="n">
-        <v>6826852</v>
+        <v>6826875</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12282,10 +12291,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119548827</v>
+        <v>119548604</v>
       </c>
       <c r="B115" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12298,21 +12307,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12322,10 +12331,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>480185</v>
+        <v>480319</v>
       </c>
       <c r="R115" t="n">
-        <v>6827084</v>
+        <v>6826923</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12384,10 +12393,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119548901</v>
+        <v>119548631</v>
       </c>
       <c r="B116" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12400,21 +12409,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12424,10 +12433,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>480450</v>
+        <v>480482</v>
       </c>
       <c r="R116" t="n">
-        <v>6826677</v>
+        <v>6826629</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12486,10 +12495,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119548845</v>
+        <v>119548992</v>
       </c>
       <c r="B117" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12502,21 +12511,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12526,10 +12535,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>480275</v>
+        <v>480293</v>
       </c>
       <c r="R117" t="n">
-        <v>6826975</v>
+        <v>6826928</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12588,7 +12597,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119548824</v>
+        <v>119548802</v>
       </c>
       <c r="B118" t="n">
         <v>78526</v>
@@ -12628,10 +12637,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>480160</v>
+        <v>480332</v>
       </c>
       <c r="R118" t="n">
-        <v>6827090</v>
+        <v>6826852</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12690,10 +12699,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119548964</v>
+        <v>119548827</v>
       </c>
       <c r="B119" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12702,25 +12711,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12730,10 +12739,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>480219</v>
+        <v>480185</v>
       </c>
       <c r="R119" t="n">
-        <v>6826902</v>
+        <v>6827084</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12792,10 +12801,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119548954</v>
+        <v>119548901</v>
       </c>
       <c r="B120" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12804,47 +12813,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>480107</v>
+        <v>480450</v>
       </c>
       <c r="R120" t="n">
-        <v>6826990</v>
+        <v>6826677</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12903,7 +12903,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119548897</v>
+        <v>119548845</v>
       </c>
       <c r="B121" t="n">
         <v>78526</v>
@@ -12943,10 +12943,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>480504</v>
+        <v>480275</v>
       </c>
       <c r="R121" t="n">
-        <v>6826757</v>
+        <v>6826975</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13005,7 +13005,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119548879</v>
+        <v>119548824</v>
       </c>
       <c r="B122" t="n">
         <v>78526</v>
@@ -13045,10 +13045,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>480367</v>
+        <v>480160</v>
       </c>
       <c r="R122" t="n">
-        <v>6826875</v>
+        <v>6827090</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13107,10 +13107,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119548736</v>
+        <v>119548621</v>
       </c>
       <c r="B123" t="n">
-        <v>78263</v>
+        <v>78560</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13123,21 +13123,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13147,10 +13147,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>480143</v>
+        <v>480425</v>
       </c>
       <c r="R123" t="n">
-        <v>6826960</v>
+        <v>6826841</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13209,7 +13209,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119548817</v>
+        <v>119548793</v>
       </c>
       <c r="B124" t="n">
         <v>78526</v>
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>480145</v>
+        <v>480514</v>
       </c>
       <c r="R124" t="n">
-        <v>6826961</v>
+        <v>6826733</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13311,7 +13311,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119548838</v>
+        <v>119548828</v>
       </c>
       <c r="B125" t="n">
         <v>78526</v>
@@ -13351,10 +13351,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>480207</v>
+        <v>480217</v>
       </c>
       <c r="R125" t="n">
-        <v>6827008</v>
+        <v>6827061</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13413,10 +13413,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119548621</v>
+        <v>119548880</v>
       </c>
       <c r="B126" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13429,21 +13429,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13453,10 +13453,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>480425</v>
+        <v>480375</v>
       </c>
       <c r="R126" t="n">
-        <v>6826841</v>
+        <v>6826874</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13515,10 +13515,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119549011</v>
+        <v>119548672</v>
       </c>
       <c r="B127" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13531,21 +13531,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13555,10 +13555,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>480353</v>
+        <v>480476</v>
       </c>
       <c r="R127" t="n">
-        <v>6826666</v>
+        <v>6826268</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13617,10 +13617,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119548672</v>
+        <v>119548971</v>
       </c>
       <c r="B128" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13629,25 +13629,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13657,10 +13657,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>480476</v>
+        <v>480497</v>
       </c>
       <c r="R128" t="n">
-        <v>6826268</v>
+        <v>6826295</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13719,7 +13719,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119548971</v>
+        <v>119548958</v>
       </c>
       <c r="B129" t="n">
         <v>91840</v>
@@ -13752,17 +13752,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>480497</v>
+        <v>480401</v>
       </c>
       <c r="R129" t="n">
-        <v>6826295</v>
+        <v>6826695</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13821,10 +13830,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119548702</v>
+        <v>119548967</v>
       </c>
       <c r="B130" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13833,25 +13842,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13861,10 +13870,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>480103</v>
+        <v>480322</v>
       </c>
       <c r="R130" t="n">
-        <v>6827007</v>
+        <v>6826949</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13923,10 +13932,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119548712</v>
+        <v>119548817</v>
       </c>
       <c r="B131" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13939,43 +13948,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>480256</v>
+        <v>480145</v>
       </c>
       <c r="R131" t="n">
-        <v>6826918</v>
+        <v>6826961</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14034,7 +14034,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119548793</v>
+        <v>119548838</v>
       </c>
       <c r="B132" t="n">
         <v>78526</v>
@@ -14074,10 +14074,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>480514</v>
+        <v>480207</v>
       </c>
       <c r="R132" t="n">
-        <v>6826733</v>
+        <v>6827008</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14136,10 +14136,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119548828</v>
+        <v>119548702</v>
       </c>
       <c r="B133" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14152,21 +14152,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14176,10 +14176,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>480217</v>
+        <v>480103</v>
       </c>
       <c r="R133" t="n">
-        <v>6827061</v>
+        <v>6827007</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14238,10 +14238,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119548880</v>
+        <v>119548736</v>
       </c>
       <c r="B134" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14254,21 +14254,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14278,10 +14278,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>480375</v>
+        <v>480143</v>
       </c>
       <c r="R134" t="n">
-        <v>6826874</v>
+        <v>6826960</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14340,10 +14340,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119548958</v>
+        <v>119549011</v>
       </c>
       <c r="B135" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14352,47 +14352,38 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>480401</v>
+        <v>480353</v>
       </c>
       <c r="R135" t="n">
-        <v>6826695</v>
+        <v>6826666</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14451,10 +14442,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119548967</v>
+        <v>119548712</v>
       </c>
       <c r="B136" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14463,38 +14454,47 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>480322</v>
+        <v>480256</v>
       </c>
       <c r="R136" t="n">
-        <v>6826949</v>
+        <v>6826918</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14553,7 +14553,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119548875</v>
+        <v>119548809</v>
       </c>
       <c r="B137" t="n">
         <v>78526</v>
@@ -14593,10 +14593,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>480351</v>
+        <v>480194</v>
       </c>
       <c r="R137" t="n">
-        <v>6826904</v>
+        <v>6826929</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14655,10 +14655,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119548853</v>
+        <v>119548652</v>
       </c>
       <c r="B138" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14671,21 +14671,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14695,10 +14695,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>480279</v>
+        <v>480499</v>
       </c>
       <c r="R138" t="n">
-        <v>6826957</v>
+        <v>6826449</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14757,7 +14757,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119548796</v>
+        <v>119548886</v>
       </c>
       <c r="B139" t="n">
         <v>78526</v>
@@ -14797,10 +14797,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>480409</v>
+        <v>480416</v>
       </c>
       <c r="R139" t="n">
-        <v>6826806</v>
+        <v>6826845</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14859,7 +14859,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119548849</v>
+        <v>119548834</v>
       </c>
       <c r="B140" t="n">
         <v>78526</v>
@@ -14899,10 +14899,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>480249</v>
+        <v>480182</v>
       </c>
       <c r="R140" t="n">
-        <v>6826948</v>
+        <v>6827039</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14961,10 +14961,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119548825</v>
+        <v>119548603</v>
       </c>
       <c r="B141" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14977,21 +14977,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15001,10 +15001,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>480165</v>
+        <v>480411</v>
       </c>
       <c r="R141" t="n">
-        <v>6827078</v>
+        <v>6826803</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15063,10 +15063,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119548809</v>
+        <v>119548608</v>
       </c>
       <c r="B142" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15079,21 +15079,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15103,10 +15103,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>480194</v>
+        <v>480248</v>
       </c>
       <c r="R142" t="n">
-        <v>6826929</v>
+        <v>6827000</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15165,10 +15165,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119548652</v>
+        <v>119548628</v>
       </c>
       <c r="B143" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15181,21 +15181,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15205,10 +15205,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>480499</v>
+        <v>480474</v>
       </c>
       <c r="R143" t="n">
-        <v>6826449</v>
+        <v>6826656</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15267,10 +15267,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119548970</v>
+        <v>119548612</v>
       </c>
       <c r="B144" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15279,25 +15279,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15307,10 +15307,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>480502</v>
+        <v>480326</v>
       </c>
       <c r="R144" t="n">
-        <v>6826561</v>
+        <v>6826964</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15369,10 +15369,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119548944</v>
+        <v>119548875</v>
       </c>
       <c r="B145" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15381,47 +15381,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>480164</v>
+        <v>480351</v>
       </c>
       <c r="R145" t="n">
-        <v>6827086</v>
+        <v>6826904</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15480,10 +15471,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119548972</v>
+        <v>119548853</v>
       </c>
       <c r="B146" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15492,25 +15483,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15520,10 +15511,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>480474</v>
+        <v>480279</v>
       </c>
       <c r="R146" t="n">
-        <v>6826272</v>
+        <v>6826957</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15582,10 +15573,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119548727</v>
+        <v>119548796</v>
       </c>
       <c r="B147" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15594,25 +15585,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15622,10 +15613,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>480224</v>
+        <v>480409</v>
       </c>
       <c r="R147" t="n">
-        <v>6827082</v>
+        <v>6826806</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15684,10 +15675,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119548603</v>
+        <v>119548849</v>
       </c>
       <c r="B148" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15700,21 +15691,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15724,10 +15715,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>480411</v>
+        <v>480249</v>
       </c>
       <c r="R148" t="n">
-        <v>6826803</v>
+        <v>6826948</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15786,10 +15777,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119548608</v>
+        <v>119548825</v>
       </c>
       <c r="B149" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15802,21 +15793,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15826,10 +15817,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>480248</v>
+        <v>480165</v>
       </c>
       <c r="R149" t="n">
-        <v>6827000</v>
+        <v>6827078</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15888,10 +15879,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119548628</v>
+        <v>119548970</v>
       </c>
       <c r="B150" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15900,25 +15891,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15928,10 +15919,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>480474</v>
+        <v>480502</v>
       </c>
       <c r="R150" t="n">
-        <v>6826656</v>
+        <v>6826561</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15990,10 +15981,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119548612</v>
+        <v>119548944</v>
       </c>
       <c r="B151" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16002,38 +15993,47 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>480326</v>
+        <v>480164</v>
       </c>
       <c r="R151" t="n">
-        <v>6826964</v>
+        <v>6827086</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16092,10 +16092,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119548886</v>
+        <v>119548972</v>
       </c>
       <c r="B152" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16104,25 +16104,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16132,10 +16132,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>480416</v>
+        <v>480474</v>
       </c>
       <c r="R152" t="n">
-        <v>6826845</v>
+        <v>6826272</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16194,10 +16194,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119548834</v>
+        <v>119548727</v>
       </c>
       <c r="B153" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16206,25 +16206,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16234,10 +16234,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>480182</v>
+        <v>480224</v>
       </c>
       <c r="R153" t="n">
-        <v>6827039</v>
+        <v>6827082</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -19272,7 +19272,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119548826</v>
+        <v>119548855</v>
       </c>
       <c r="B183" t="n">
         <v>78526</v>
@@ -19312,10 +19312,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>480183</v>
+        <v>480298</v>
       </c>
       <c r="R183" t="n">
-        <v>6827072</v>
+        <v>6826971</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19374,7 +19374,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119548908</v>
+        <v>119548851</v>
       </c>
       <c r="B184" t="n">
         <v>78526</v>
@@ -19414,10 +19414,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>480478</v>
+        <v>480258</v>
       </c>
       <c r="R184" t="n">
-        <v>6826636</v>
+        <v>6826942</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19476,10 +19476,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119548941</v>
+        <v>119548850</v>
       </c>
       <c r="B185" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19488,47 +19488,38 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>480113</v>
+        <v>480253</v>
       </c>
       <c r="R185" t="n">
-        <v>6826982</v>
+        <v>6826941</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19587,10 +19578,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119548930</v>
+        <v>119548830</v>
       </c>
       <c r="B186" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19599,47 +19590,38 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>480228</v>
+        <v>480214</v>
       </c>
       <c r="R186" t="n">
-        <v>6827065</v>
+        <v>6827047</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19698,10 +19680,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119548961</v>
+        <v>119548868</v>
       </c>
       <c r="B187" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19710,25 +19692,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19738,10 +19720,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>480508</v>
+        <v>480343</v>
       </c>
       <c r="R187" t="n">
-        <v>6826508</v>
+        <v>6826936</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19800,10 +19782,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119548755</v>
+        <v>119548812</v>
       </c>
       <c r="B188" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19816,21 +19798,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19840,7 +19822,7 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>480273</v>
+        <v>480181</v>
       </c>
       <c r="R188" t="n">
         <v>6826939</v>
@@ -19902,7 +19884,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119548855</v>
+        <v>119548899</v>
       </c>
       <c r="B189" t="n">
         <v>78526</v>
@@ -19942,10 +19924,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>480298</v>
+        <v>480438</v>
       </c>
       <c r="R189" t="n">
-        <v>6826971</v>
+        <v>6826705</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20004,10 +19986,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119548851</v>
+        <v>119548941</v>
       </c>
       <c r="B190" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20016,38 +19998,47 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>480258</v>
+        <v>480113</v>
       </c>
       <c r="R190" t="n">
-        <v>6826942</v>
+        <v>6826982</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20106,10 +20097,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119548850</v>
+        <v>119548930</v>
       </c>
       <c r="B191" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20118,38 +20109,47 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>480253</v>
+        <v>480228</v>
       </c>
       <c r="R191" t="n">
-        <v>6826941</v>
+        <v>6827065</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20208,10 +20208,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119548830</v>
+        <v>119548961</v>
       </c>
       <c r="B192" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20220,25 +20220,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20248,10 +20248,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>480214</v>
+        <v>480508</v>
       </c>
       <c r="R192" t="n">
-        <v>6827047</v>
+        <v>6826508</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20310,10 +20310,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119548868</v>
+        <v>119548755</v>
       </c>
       <c r="B193" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20326,21 +20326,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20350,10 +20350,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>480343</v>
+        <v>480273</v>
       </c>
       <c r="R193" t="n">
-        <v>6826936</v>
+        <v>6826939</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20412,7 +20412,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119548812</v>
+        <v>119548826</v>
       </c>
       <c r="B194" t="n">
         <v>78526</v>
@@ -20452,10 +20452,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>480181</v>
+        <v>480183</v>
       </c>
       <c r="R194" t="n">
-        <v>6826939</v>
+        <v>6827072</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20514,7 +20514,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119548899</v>
+        <v>119548908</v>
       </c>
       <c r="B195" t="n">
         <v>78526</v>
@@ -20554,10 +20554,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>480438</v>
+        <v>480478</v>
       </c>
       <c r="R195" t="n">
-        <v>6826705</v>
+        <v>6826636</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20616,10 +20616,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119548710</v>
+        <v>119548615</v>
       </c>
       <c r="B196" t="n">
-        <v>91884</v>
+        <v>78560</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20632,43 +20632,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5449</v>
+        <v>185</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>480374</v>
+        <v>480367</v>
       </c>
       <c r="R196" t="n">
-        <v>6826894</v>
+        <v>6826868</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20727,10 +20718,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119548715</v>
+        <v>119548709</v>
       </c>
       <c r="B197" t="n">
-        <v>91884</v>
+        <v>91463</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20743,21 +20734,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20767,10 +20758,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>480513</v>
+        <v>480356</v>
       </c>
       <c r="R197" t="n">
-        <v>6826505</v>
+        <v>6826904</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20829,10 +20820,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119548790</v>
+        <v>119548710</v>
       </c>
       <c r="B198" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20845,34 +20836,43 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>480589</v>
+        <v>480374</v>
       </c>
       <c r="R198" t="n">
-        <v>6826666</v>
+        <v>6826894</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20931,7 +20931,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119548786</v>
+        <v>119548890</v>
       </c>
       <c r="B199" t="n">
         <v>78526</v>
@@ -20971,10 +20971,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>480553</v>
+        <v>480454</v>
       </c>
       <c r="R199" t="n">
-        <v>6826623</v>
+        <v>6826841</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21033,7 +21033,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119548895</v>
+        <v>119548801</v>
       </c>
       <c r="B200" t="n">
         <v>78526</v>
@@ -21073,10 +21073,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>480486</v>
+        <v>480314</v>
       </c>
       <c r="R200" t="n">
-        <v>6826811</v>
+        <v>6826847</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21135,10 +21135,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119548615</v>
+        <v>119548892</v>
       </c>
       <c r="B201" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21151,21 +21151,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21175,10 +21175,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>480367</v>
+        <v>480462</v>
       </c>
       <c r="R201" t="n">
-        <v>6826868</v>
+        <v>6826805</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21237,10 +21237,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119548709</v>
+        <v>119548787</v>
       </c>
       <c r="B202" t="n">
-        <v>91463</v>
+        <v>78526</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21253,21 +21253,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21277,10 +21277,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>480356</v>
+        <v>480563</v>
       </c>
       <c r="R202" t="n">
-        <v>6826904</v>
+        <v>6826626</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21339,10 +21339,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119548890</v>
+        <v>119548715</v>
       </c>
       <c r="B203" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21355,21 +21355,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21379,10 +21379,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>480454</v>
+        <v>480513</v>
       </c>
       <c r="R203" t="n">
-        <v>6826841</v>
+        <v>6826505</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21441,7 +21441,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119548801</v>
+        <v>119548790</v>
       </c>
       <c r="B204" t="n">
         <v>78526</v>
@@ -21481,10 +21481,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>480314</v>
+        <v>480589</v>
       </c>
       <c r="R204" t="n">
-        <v>6826847</v>
+        <v>6826666</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21543,7 +21543,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119548892</v>
+        <v>119548786</v>
       </c>
       <c r="B205" t="n">
         <v>78526</v>
@@ -21583,10 +21583,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>480462</v>
+        <v>480553</v>
       </c>
       <c r="R205" t="n">
-        <v>6826805</v>
+        <v>6826623</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21645,7 +21645,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119548787</v>
+        <v>119548895</v>
       </c>
       <c r="B206" t="n">
         <v>78526</v>
@@ -21685,10 +21685,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>480563</v>
+        <v>480486</v>
       </c>
       <c r="R206" t="n">
-        <v>6826626</v>
+        <v>6826811</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24555,10 +24555,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>119548746</v>
+        <v>119548609</v>
       </c>
       <c r="B234" t="n">
-        <v>78262</v>
+        <v>78560</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24571,21 +24571,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -24595,10 +24595,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>480481</v>
+        <v>480266</v>
       </c>
       <c r="R234" t="n">
-        <v>6826375</v>
+        <v>6826970</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24657,10 +24657,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119548609</v>
+        <v>119548996</v>
       </c>
       <c r="B235" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24673,21 +24673,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24697,10 +24697,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>480266</v>
+        <v>480115</v>
       </c>
       <c r="R235" t="n">
-        <v>6826970</v>
+        <v>6827003</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24759,7 +24759,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>119548996</v>
+        <v>119548999</v>
       </c>
       <c r="B236" t="n">
         <v>78171</v>
@@ -24799,10 +24799,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>480115</v>
+        <v>480108</v>
       </c>
       <c r="R236" t="n">
-        <v>6827003</v>
+        <v>6827038</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24861,10 +24861,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>119548999</v>
+        <v>119548883</v>
       </c>
       <c r="B237" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24877,21 +24877,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24901,10 +24901,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>480108</v>
+        <v>480363</v>
       </c>
       <c r="R237" t="n">
-        <v>6827038</v>
+        <v>6826853</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24963,7 +24963,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>119548883</v>
+        <v>119548857</v>
       </c>
       <c r="B238" t="n">
         <v>78526</v>
@@ -25003,10 +25003,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>480363</v>
+        <v>480295</v>
       </c>
       <c r="R238" t="n">
-        <v>6826853</v>
+        <v>6826987</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25065,7 +25065,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>119548857</v>
+        <v>119548791</v>
       </c>
       <c r="B239" t="n">
         <v>78526</v>
@@ -25105,10 +25105,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>480295</v>
+        <v>480585</v>
       </c>
       <c r="R239" t="n">
-        <v>6826987</v>
+        <v>6826740</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25167,7 +25167,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>119548791</v>
+        <v>119548808</v>
       </c>
       <c r="B240" t="n">
         <v>78526</v>
@@ -25207,10 +25207,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>480585</v>
+        <v>480210</v>
       </c>
       <c r="R240" t="n">
-        <v>6826740</v>
+        <v>6826906</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25269,10 +25269,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>119548808</v>
+        <v>119548951</v>
       </c>
       <c r="B241" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25281,38 +25281,47 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>480210</v>
+        <v>480122</v>
       </c>
       <c r="R241" t="n">
-        <v>6826906</v>
+        <v>6827072</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25371,10 +25380,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>119548951</v>
+        <v>119548746</v>
       </c>
       <c r="B242" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25383,47 +25392,38 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>480122</v>
+        <v>480481</v>
       </c>
       <c r="R242" t="n">
-        <v>6827072</v>
+        <v>6826375</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28751,7 +28751,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>119579998</v>
+        <v>119583506</v>
       </c>
       <c r="B274" t="n">
         <v>91840</v>
@@ -28787,14 +28787,14 @@
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>480486</v>
+        <v>480596</v>
       </c>
       <c r="R274" t="n">
-        <v>6827011</v>
+        <v>6827018</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28853,10 +28853,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>119583506</v>
+        <v>119583220</v>
       </c>
       <c r="B275" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -28865,25 +28865,25 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28893,10 +28893,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>480596</v>
+        <v>480667</v>
       </c>
       <c r="R275" t="n">
-        <v>6827018</v>
+        <v>6826982</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28955,10 +28955,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>119579045</v>
+        <v>119581533</v>
       </c>
       <c r="B276" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -28971,34 +28971,34 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>480435</v>
+        <v>480528</v>
       </c>
       <c r="R276" t="n">
-        <v>6827020</v>
+        <v>6826796</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -29057,10 +29057,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>119583220</v>
+        <v>119579045</v>
       </c>
       <c r="B277" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -29073,34 +29073,34 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>480667</v>
+        <v>480435</v>
       </c>
       <c r="R277" t="n">
-        <v>6826982</v>
+        <v>6827020</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -29159,10 +29159,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>119581533</v>
+        <v>119579998</v>
       </c>
       <c r="B278" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -29171,38 +29171,38 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>480528</v>
+        <v>480486</v>
       </c>
       <c r="R278" t="n">
-        <v>6826796</v>
+        <v>6827011</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -29990,10 +29990,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>119580566</v>
+        <v>119582035</v>
       </c>
       <c r="B286" t="n">
-        <v>91834</v>
+        <v>78263</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -30006,43 +30006,34 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>480597</v>
+        <v>480510</v>
       </c>
       <c r="R286" t="n">
-        <v>6826933</v>
+        <v>6826812</v>
       </c>
       <c r="S286" t="n">
         <v>9</v>
@@ -30074,7 +30065,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -30084,7 +30075,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -30111,10 +30102,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>119582752</v>
+        <v>119580566</v>
       </c>
       <c r="B287" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -30123,38 +30114,47 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>480624</v>
+        <v>480597</v>
       </c>
       <c r="R287" t="n">
-        <v>6826698</v>
+        <v>6826933</v>
       </c>
       <c r="S287" t="n">
         <v>9</v>
@@ -30186,7 +30186,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -30196,7 +30196,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -30223,10 +30223,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>119582425</v>
+        <v>119582752</v>
       </c>
       <c r="B288" t="n">
-        <v>90580</v>
+        <v>91840</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -30235,41 +30235,41 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>480725</v>
+        <v>480624</v>
       </c>
       <c r="R288" t="n">
-        <v>6826708</v>
+        <v>6826698</v>
       </c>
       <c r="S288" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -30296,9 +30296,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA288" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -30313,22 +30323,22 @@
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>119582035</v>
+        <v>119582425</v>
       </c>
       <c r="B289" t="n">
-        <v>78263</v>
+        <v>90580</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -30341,37 +30351,37 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>480510</v>
+        <v>480725</v>
       </c>
       <c r="R289" t="n">
-        <v>6826812</v>
+        <v>6826708</v>
       </c>
       <c r="S289" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -30398,19 +30408,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z289" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA289" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -30425,12 +30425,12 @@
       <c r="AT289" t="inlineStr"/>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
@@ -30549,10 +30549,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>119581193</v>
+        <v>119582896</v>
       </c>
       <c r="B291" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -30561,41 +30561,41 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>480559</v>
+        <v>480697</v>
       </c>
       <c r="R291" t="n">
-        <v>6826841</v>
+        <v>6826827</v>
       </c>
       <c r="S291" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
@@ -30622,19 +30622,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z291" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA291" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB291" t="inlineStr">
-        <is>
-          <t>12:53</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -30649,22 +30639,22 @@
       <c r="AT291" t="inlineStr"/>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>119582896</v>
+        <v>119581193</v>
       </c>
       <c r="B292" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -30673,41 +30663,41 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>480697</v>
+        <v>480559</v>
       </c>
       <c r="R292" t="n">
-        <v>6826827</v>
+        <v>6826841</v>
       </c>
       <c r="S292" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T292" t="inlineStr">
         <is>
@@ -30734,9 +30724,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA292" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB292" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD292" t="b">
@@ -30751,22 +30751,22 @@
       <c r="AT292" t="inlineStr"/>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>119582210</v>
+        <v>119582239</v>
       </c>
       <c r="B293" t="n">
-        <v>91884</v>
+        <v>74638</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -30779,46 +30779,37 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>5449</v>
+        <v>6440</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>480495</v>
+        <v>480668</v>
       </c>
       <c r="R293" t="n">
-        <v>6826796</v>
+        <v>6826697</v>
       </c>
       <c r="S293" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
@@ -30845,19 +30836,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z293" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA293" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB293" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -30872,22 +30853,22 @@
       <c r="AT293" t="inlineStr"/>
       <c r="AW293" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>119578964</v>
+        <v>119583227</v>
       </c>
       <c r="B294" t="n">
-        <v>91856</v>
+        <v>78262</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -30900,43 +30881,34 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>480378</v>
+        <v>480664</v>
       </c>
       <c r="R294" t="n">
-        <v>6827025</v>
+        <v>6826993</v>
       </c>
       <c r="S294" t="n">
         <v>9</v>
@@ -30968,7 +30940,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -30978,7 +30950,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -31005,10 +30977,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>119582910</v>
+        <v>119581051</v>
       </c>
       <c r="B295" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -31017,41 +30989,41 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>480778</v>
+        <v>480544</v>
       </c>
       <c r="R295" t="n">
-        <v>6826820</v>
+        <v>6826852</v>
       </c>
       <c r="S295" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -31078,19 +31050,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z295" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA295" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB295" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -31105,22 +31067,22 @@
       <c r="AT295" t="inlineStr"/>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>119582239</v>
+        <v>119578964</v>
       </c>
       <c r="B296" t="n">
-        <v>74638</v>
+        <v>91856</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -31133,37 +31095,46 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6440</v>
+        <v>2059</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>480668</v>
+        <v>480378</v>
       </c>
       <c r="R296" t="n">
-        <v>6826697</v>
+        <v>6827025</v>
       </c>
       <c r="S296" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -31190,9 +31161,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA296" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -31207,22 +31188,22 @@
       <c r="AT296" t="inlineStr"/>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>119583227</v>
+        <v>119582910</v>
       </c>
       <c r="B297" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -31231,25 +31212,25 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -31259,10 +31240,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>480664</v>
+        <v>480778</v>
       </c>
       <c r="R297" t="n">
-        <v>6826993</v>
+        <v>6826820</v>
       </c>
       <c r="S297" t="n">
         <v>9</v>
@@ -31294,7 +31275,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -31304,7 +31285,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -31331,10 +31312,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>119581051</v>
+        <v>119582210</v>
       </c>
       <c r="B298" t="n">
-        <v>78262</v>
+        <v>91884</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -31347,37 +31328,46 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>480544</v>
+        <v>480495</v>
       </c>
       <c r="R298" t="n">
-        <v>6826852</v>
+        <v>6826796</v>
       </c>
       <c r="S298" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
@@ -31404,9 +31394,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA298" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -31421,12 +31421,12 @@
       <c r="AT298" t="inlineStr"/>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
@@ -33204,10 +33204,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>119591279</v>
+        <v>119591275</v>
       </c>
       <c r="B316" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -33216,25 +33216,25 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
@@ -33244,10 +33244,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>480470</v>
+        <v>480440</v>
       </c>
       <c r="R316" t="n">
-        <v>6826996</v>
+        <v>6826986</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -33306,10 +33306,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>119591275</v>
+        <v>119591279</v>
       </c>
       <c r="B317" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -33318,25 +33318,25 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
@@ -33346,10 +33346,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>480440</v>
+        <v>480470</v>
       </c>
       <c r="R317" t="n">
-        <v>6826986</v>
+        <v>6826996</v>
       </c>
       <c r="S317" t="n">
         <v>10</v>
@@ -34452,10 +34452,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>119672825</v>
+        <v>119672811</v>
       </c>
       <c r="B328" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -34464,25 +34464,25 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
@@ -34492,10 +34492,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>480611</v>
+        <v>480600</v>
       </c>
       <c r="R328" t="n">
-        <v>6826826</v>
+        <v>6826809</v>
       </c>
       <c r="S328" t="n">
         <v>1</v>
@@ -34530,6 +34530,11 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC328" t="inlineStr">
+        <is>
+          <t>Timmergröppa</t>
+        </is>
+      </c>
       <c r="AD328" t="b">
         <v>0</v>
       </c>
@@ -34547,17 +34552,17 @@
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Erik Danielsson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>119672811</v>
+        <v>119672825</v>
       </c>
       <c r="B329" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -34566,25 +34571,25 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
@@ -34594,10 +34599,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>480600</v>
+        <v>480611</v>
       </c>
       <c r="R329" t="n">
-        <v>6826809</v>
+        <v>6826826</v>
       </c>
       <c r="S329" t="n">
         <v>1</v>
@@ -34632,11 +34637,6 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC329" t="inlineStr">
-        <is>
-          <t>Timmergröppa</t>
-        </is>
-      </c>
       <c r="AD329" t="b">
         <v>0</v>
       </c>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>Erik Danielsson, Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
@@ -36707,10 +36707,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>119710922</v>
+        <v>119710918</v>
       </c>
       <c r="B350" t="n">
-        <v>78263</v>
+        <v>56522</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -36719,38 +36719,50 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr"/>
       <c r="P350" t="inlineStr">
         <is>
           <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>480596</v>
+        <v>480604</v>
       </c>
       <c r="R350" t="n">
-        <v>6826803</v>
+        <v>6826853</v>
       </c>
       <c r="S350" t="n">
         <v>10</v>
@@ -36809,10 +36821,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>119710927</v>
+        <v>119710922</v>
       </c>
       <c r="B351" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -36825,21 +36837,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I351" t="inlineStr"/>
@@ -36849,10 +36861,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>480320</v>
+        <v>480596</v>
       </c>
       <c r="R351" t="n">
-        <v>6826981</v>
+        <v>6826803</v>
       </c>
       <c r="S351" t="n">
         <v>10</v>
@@ -36911,10 +36923,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>119710918</v>
+        <v>119710927</v>
       </c>
       <c r="B352" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -36923,50 +36935,38 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr"/>
-      <c r="L352" t="inlineStr"/>
-      <c r="M352" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N352" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
           <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>480604</v>
+        <v>480320</v>
       </c>
       <c r="R352" t="n">
-        <v>6826853</v>
+        <v>6826981</v>
       </c>
       <c r="S352" t="n">
         <v>10</v>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -25603,10 +25603,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>119580536</v>
+        <v>119578984</v>
       </c>
       <c r="B244" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25619,21 +25619,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25643,10 +25643,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>480603</v>
+        <v>480389</v>
       </c>
       <c r="R244" t="n">
-        <v>6826946</v>
+        <v>6827030</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25705,10 +25705,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>119580925</v>
+        <v>119581533</v>
       </c>
       <c r="B245" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25717,25 +25717,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25745,10 +25745,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>480579</v>
+        <v>480528</v>
       </c>
       <c r="R245" t="n">
-        <v>6826835</v>
+        <v>6826796</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25807,10 +25807,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>119578984</v>
+        <v>119580536</v>
       </c>
       <c r="B246" t="n">
-        <v>91884</v>
+        <v>79144</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25823,21 +25823,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25847,10 +25847,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>480389</v>
+        <v>480603</v>
       </c>
       <c r="R246" t="n">
-        <v>6827030</v>
+        <v>6826946</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25909,10 +25909,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>119581533</v>
+        <v>119580925</v>
       </c>
       <c r="B247" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25921,25 +25921,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25949,10 +25949,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>480528</v>
+        <v>480579</v>
       </c>
       <c r="R247" t="n">
-        <v>6826796</v>
+        <v>6826835</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26011,10 +26011,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>119580566</v>
+        <v>119583044</v>
       </c>
       <c r="B248" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26023,47 +26023,38 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>480597</v>
+        <v>480711</v>
       </c>
       <c r="R248" t="n">
-        <v>6826933</v>
+        <v>6826881</v>
       </c>
       <c r="S248" t="n">
         <v>9</v>
@@ -26095,7 +26086,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -26105,7 +26096,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26132,10 +26123,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>119583044</v>
+        <v>119579902</v>
       </c>
       <c r="B249" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26144,38 +26135,47 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>480711</v>
+        <v>480490</v>
       </c>
       <c r="R249" t="n">
-        <v>6826881</v>
+        <v>6827006</v>
       </c>
       <c r="S249" t="n">
         <v>9</v>
@@ -26207,7 +26207,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26244,7 +26244,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>119579902</v>
+        <v>119580566</v>
       </c>
       <c r="B250" t="n">
         <v>91834</v>
@@ -26293,10 +26293,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>480490</v>
+        <v>480597</v>
       </c>
       <c r="R250" t="n">
-        <v>6827006</v>
+        <v>6826933</v>
       </c>
       <c r="S250" t="n">
         <v>9</v>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -26338,7 +26338,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26365,10 +26365,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>119581710</v>
+        <v>119583116</v>
       </c>
       <c r="B251" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26377,41 +26377,41 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>480505</v>
+        <v>480685</v>
       </c>
       <c r="R251" t="n">
-        <v>6826739</v>
+        <v>6826946</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26438,9 +26438,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26455,22 +26465,22 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>119583116</v>
+        <v>119580034</v>
       </c>
       <c r="B252" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26479,38 +26489,47 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P252" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>480685</v>
+        <v>480490</v>
       </c>
       <c r="R252" t="n">
-        <v>6826946</v>
+        <v>6827012</v>
       </c>
       <c r="S252" t="n">
         <v>9</v>
@@ -26542,7 +26561,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -26552,7 +26571,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -26579,10 +26598,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>119580034</v>
+        <v>119583019</v>
       </c>
       <c r="B253" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26591,50 +26610,41 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>480490</v>
+        <v>480716</v>
       </c>
       <c r="R253" t="n">
-        <v>6827012</v>
+        <v>6826851</v>
       </c>
       <c r="S253" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -26661,19 +26671,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>11:56</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -26688,22 +26688,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>119583019</v>
+        <v>119581710</v>
       </c>
       <c r="B254" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26712,25 +26712,25 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26740,10 +26740,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>480716</v>
+        <v>480505</v>
       </c>
       <c r="R254" t="n">
-        <v>6826851</v>
+        <v>6826739</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -27108,10 +27108,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>119578834</v>
+        <v>119583220</v>
       </c>
       <c r="B258" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27124,34 +27124,34 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>480414</v>
+        <v>480667</v>
       </c>
       <c r="R258" t="n">
-        <v>6827025</v>
+        <v>6826982</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27210,10 +27210,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>119583220</v>
+        <v>119578834</v>
       </c>
       <c r="B259" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27226,34 +27226,34 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>480667</v>
+        <v>480414</v>
       </c>
       <c r="R259" t="n">
-        <v>6826982</v>
+        <v>6827025</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27827,10 +27827,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>119582239</v>
+        <v>119582910</v>
       </c>
       <c r="B265" t="n">
-        <v>74638</v>
+        <v>91840</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27839,41 +27839,41 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>480668</v>
+        <v>480778</v>
       </c>
       <c r="R265" t="n">
-        <v>6826697</v>
+        <v>6826820</v>
       </c>
       <c r="S265" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -27900,9 +27900,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -27917,22 +27927,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>119582030</v>
+        <v>119578713</v>
       </c>
       <c r="B266" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27945,37 +27955,37 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>480509</v>
+        <v>480386</v>
       </c>
       <c r="R266" t="n">
-        <v>6826812</v>
+        <v>6826995</v>
       </c>
       <c r="S266" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -28002,19 +28012,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28029,22 +28029,22 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>119582910</v>
+        <v>119582239</v>
       </c>
       <c r="B267" t="n">
-        <v>91840</v>
+        <v>74638</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28053,41 +28053,41 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>480778</v>
+        <v>480668</v>
       </c>
       <c r="R267" t="n">
-        <v>6826820</v>
+        <v>6826697</v>
       </c>
       <c r="S267" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -28114,19 +28114,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28141,22 +28131,22 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>119578713</v>
+        <v>119582030</v>
       </c>
       <c r="B268" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28169,37 +28159,37 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>480386</v>
+        <v>480509</v>
       </c>
       <c r="R268" t="n">
-        <v>6826995</v>
+        <v>6826812</v>
       </c>
       <c r="S268" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28226,9 +28216,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28243,12 +28243,12 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
@@ -28784,10 +28784,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>119579158</v>
+        <v>119582035</v>
       </c>
       <c r="B274" t="n">
-        <v>89633</v>
+        <v>78263</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28800,37 +28800,37 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>480467</v>
+        <v>480510</v>
       </c>
       <c r="R274" t="n">
-        <v>6827000</v>
+        <v>6826812</v>
       </c>
       <c r="S274" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -28857,9 +28857,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA274" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -28874,22 +28884,22 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>119581176</v>
+        <v>119579158</v>
       </c>
       <c r="B275" t="n">
-        <v>57310</v>
+        <v>89633</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -28902,42 +28912,37 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>480542</v>
+        <v>480467</v>
       </c>
       <c r="R275" t="n">
-        <v>6826841</v>
+        <v>6827000</v>
       </c>
       <c r="S275" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -28993,10 +28998,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>119582035</v>
+        <v>119581176</v>
       </c>
       <c r="B276" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -29009,37 +29014,42 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>480510</v>
+        <v>480542</v>
       </c>
       <c r="R276" t="n">
-        <v>6826812</v>
+        <v>6826841</v>
       </c>
       <c r="S276" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -29066,19 +29076,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -29093,12 +29093,12 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
@@ -29217,10 +29217,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>119583661</v>
+        <v>119579998</v>
       </c>
       <c r="B278" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -29229,41 +29229,41 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>480558</v>
+        <v>480486</v>
       </c>
       <c r="R278" t="n">
-        <v>6827045</v>
+        <v>6827011</v>
       </c>
       <c r="S278" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -29290,24 +29290,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z278" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB278" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC278" t="inlineStr">
-        <is>
-          <t>På talstam</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -29322,22 +29307,22 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>119579998</v>
+        <v>119582581</v>
       </c>
       <c r="B279" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -29346,41 +29331,41 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>480486</v>
+        <v>480554</v>
       </c>
       <c r="R279" t="n">
-        <v>6827011</v>
+        <v>6826774</v>
       </c>
       <c r="S279" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -29407,9 +29392,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA279" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -29424,22 +29419,22 @@
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>119582581</v>
+        <v>119582604</v>
       </c>
       <c r="B280" t="n">
-        <v>91834</v>
+        <v>57463</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -29452,21 +29447,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -29482,7 +29477,7 @@
         <v>6826774</v>
       </c>
       <c r="S280" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -29548,10 +29543,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>119582604</v>
+        <v>119583661</v>
       </c>
       <c r="B281" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -29564,37 +29559,37 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>480554</v>
+        <v>480558</v>
       </c>
       <c r="R281" t="n">
-        <v>6826774</v>
+        <v>6827045</v>
       </c>
       <c r="S281" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -29623,7 +29618,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -29633,7 +29628,12 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>På talstam</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -29660,10 +29660,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>119583506</v>
+        <v>119578655</v>
       </c>
       <c r="B282" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -29672,38 +29672,38 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>480596</v>
+        <v>480324</v>
       </c>
       <c r="R282" t="n">
-        <v>6827018</v>
+        <v>6826985</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -29762,10 +29762,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>119580285</v>
+        <v>119582896</v>
       </c>
       <c r="B283" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -29774,38 +29774,38 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>480531</v>
+        <v>480697</v>
       </c>
       <c r="R283" t="n">
-        <v>6827030</v>
+        <v>6826827</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29971,10 +29971,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>119578655</v>
+        <v>119583506</v>
       </c>
       <c r="B285" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -29983,38 +29983,38 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>480324</v>
+        <v>480596</v>
       </c>
       <c r="R285" t="n">
-        <v>6826985</v>
+        <v>6827018</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -30073,10 +30073,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>119582896</v>
+        <v>119580285</v>
       </c>
       <c r="B286" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -30085,38 +30085,38 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>480697</v>
+        <v>480531</v>
       </c>
       <c r="R286" t="n">
-        <v>6826827</v>
+        <v>6827030</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -31857,10 +31857,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>119611853</v>
+        <v>119611396</v>
       </c>
       <c r="B303" t="n">
-        <v>78560</v>
+        <v>91884</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -31873,34 +31873,34 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>185</v>
+        <v>5449</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
-          <t>Rävtjärn norra, Dlr</t>
+          <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>480598</v>
+        <v>480668</v>
       </c>
       <c r="R303" t="n">
-        <v>6826815</v>
+        <v>6826948</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -31935,34 +31935,40 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC303" t="inlineStr">
+        <is>
+          <t>3 fk</t>
+        </is>
+      </c>
       <c r="AD303" t="b">
         <v>0</v>
       </c>
       <c r="AE303" t="b">
         <v>0</v>
       </c>
+      <c r="AF303" t="inlineStr"/>
       <c r="AG303" t="b">
         <v>0</v>
       </c>
       <c r="AT303" t="inlineStr"/>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>119611396</v>
+        <v>119611853</v>
       </c>
       <c r="B304" t="n">
-        <v>91884</v>
+        <v>78560</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -31975,34 +31981,34 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>5449</v>
+        <v>185</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
-          <t>Rävtjärn, Dlr</t>
+          <t>Rävtjärn norra, Dlr</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>480668</v>
+        <v>480598</v>
       </c>
       <c r="R304" t="n">
-        <v>6826948</v>
+        <v>6826815</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -32037,30 +32043,24 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC304" t="inlineStr">
-        <is>
-          <t>3 fk</t>
-        </is>
-      </c>
       <c r="AD304" t="b">
         <v>0</v>
       </c>
       <c r="AE304" t="b">
         <v>0</v>
       </c>
-      <c r="AF304" t="inlineStr"/>
       <c r="AG304" t="b">
         <v>0</v>
       </c>
       <c r="AT304" t="inlineStr"/>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -25482,10 +25482,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>119582210</v>
+        <v>119579893</v>
       </c>
       <c r="B243" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25494,50 +25494,41 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>480495</v>
+        <v>480484</v>
       </c>
       <c r="R243" t="n">
-        <v>6826796</v>
+        <v>6826991</v>
       </c>
       <c r="S243" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -25564,19 +25555,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25591,22 +25572,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>119578984</v>
+        <v>119583116</v>
       </c>
       <c r="B244" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25615,41 +25596,41 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>480389</v>
+        <v>480685</v>
       </c>
       <c r="R244" t="n">
-        <v>6827030</v>
+        <v>6826946</v>
       </c>
       <c r="S244" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -25676,9 +25657,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -25693,22 +25684,22 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>119581533</v>
+        <v>119581710</v>
       </c>
       <c r="B245" t="n">
-        <v>78526</v>
+        <v>89633</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25721,21 +25712,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25745,10 +25736,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>480528</v>
+        <v>480505</v>
       </c>
       <c r="R245" t="n">
-        <v>6826796</v>
+        <v>6826739</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25807,10 +25798,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>119580536</v>
+        <v>119578713</v>
       </c>
       <c r="B246" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25823,21 +25814,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25847,10 +25838,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>480603</v>
+        <v>480386</v>
       </c>
       <c r="R246" t="n">
-        <v>6826946</v>
+        <v>6826995</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25909,10 +25900,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>119580925</v>
+        <v>119580536</v>
       </c>
       <c r="B247" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25921,38 +25912,38 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>480579</v>
+        <v>480603</v>
       </c>
       <c r="R247" t="n">
-        <v>6826835</v>
+        <v>6826946</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26011,10 +26002,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>119583044</v>
+        <v>119580910</v>
       </c>
       <c r="B248" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26023,41 +26014,41 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>480711</v>
+        <v>480590</v>
       </c>
       <c r="R248" t="n">
-        <v>6826881</v>
+        <v>6826836</v>
       </c>
       <c r="S248" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26084,19 +26075,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26111,22 +26092,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>119579902</v>
+        <v>119582030</v>
       </c>
       <c r="B249" t="n">
-        <v>91834</v>
+        <v>78262</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26139,43 +26120,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>480490</v>
+        <v>480509</v>
       </c>
       <c r="R249" t="n">
-        <v>6827006</v>
+        <v>6826812</v>
       </c>
       <c r="S249" t="n">
         <v>9</v>
@@ -26207,7 +26179,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -26217,7 +26189,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26244,10 +26216,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>119580566</v>
+        <v>119580118</v>
       </c>
       <c r="B250" t="n">
-        <v>91834</v>
+        <v>78262</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26260,46 +26232,37 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>480597</v>
+        <v>480492</v>
       </c>
       <c r="R250" t="n">
-        <v>6826933</v>
+        <v>6827031</v>
       </c>
       <c r="S250" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -26326,19 +26289,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>12:25</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26353,22 +26306,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>119583116</v>
+        <v>119579045</v>
       </c>
       <c r="B251" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26377,41 +26330,41 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>480685</v>
+        <v>480435</v>
       </c>
       <c r="R251" t="n">
-        <v>6826946</v>
+        <v>6827020</v>
       </c>
       <c r="S251" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26438,19 +26391,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26465,22 +26408,22 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>119580034</v>
+        <v>119583220</v>
       </c>
       <c r="B252" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26493,46 +26436,37 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>480490</v>
+        <v>480667</v>
       </c>
       <c r="R252" t="n">
-        <v>6827012</v>
+        <v>6826982</v>
       </c>
       <c r="S252" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -26559,19 +26493,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>11:56</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -26586,22 +26510,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>119583019</v>
+        <v>119579062</v>
       </c>
       <c r="B253" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26610,41 +26534,46 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>480716</v>
+        <v>480449</v>
       </c>
       <c r="R253" t="n">
-        <v>6826851</v>
+        <v>6826994</v>
       </c>
       <c r="S253" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -26700,7 +26629,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>119581710</v>
+        <v>119579158</v>
       </c>
       <c r="B254" t="n">
         <v>89633</v>
@@ -26736,14 +26665,14 @@
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>480505</v>
+        <v>480467</v>
       </c>
       <c r="R254" t="n">
-        <v>6826739</v>
+        <v>6827000</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26802,10 +26731,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>119581644</v>
+        <v>119581051</v>
       </c>
       <c r="B255" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26818,21 +26747,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26842,10 +26771,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>480505</v>
+        <v>480544</v>
       </c>
       <c r="R255" t="n">
-        <v>6826739</v>
+        <v>6826852</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27006,10 +26935,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>119582425</v>
+        <v>119578964</v>
       </c>
       <c r="B257" t="n">
-        <v>90580</v>
+        <v>91856</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27022,37 +26951,46 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>5432</v>
+        <v>2059</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>480725</v>
+        <v>480378</v>
       </c>
       <c r="R257" t="n">
-        <v>6826708</v>
+        <v>6827025</v>
       </c>
       <c r="S257" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -27079,9 +27017,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27096,22 +27044,22 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>119583220</v>
+        <v>119582533</v>
       </c>
       <c r="B258" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27124,21 +27072,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27148,10 +27096,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>480667</v>
+        <v>480732</v>
       </c>
       <c r="R258" t="n">
-        <v>6826982</v>
+        <v>6826736</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27210,10 +27158,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>119578834</v>
+        <v>119580034</v>
       </c>
       <c r="B259" t="n">
-        <v>78560</v>
+        <v>91834</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27226,37 +27174,46 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>185</v>
+        <v>4362</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>480414</v>
+        <v>480490</v>
       </c>
       <c r="R259" t="n">
-        <v>6827025</v>
+        <v>6827012</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -27283,9 +27240,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27300,22 +27267,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>119580118</v>
+        <v>119582623</v>
       </c>
       <c r="B260" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27328,34 +27295,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>480492</v>
+        <v>480770</v>
       </c>
       <c r="R260" t="n">
-        <v>6827031</v>
+        <v>6826753</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27414,10 +27381,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>119579045</v>
+        <v>119582028</v>
       </c>
       <c r="B261" t="n">
-        <v>78262</v>
+        <v>91886</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27426,38 +27393,38 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6446</v>
+        <v>232140</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>480435</v>
+        <v>480596</v>
       </c>
       <c r="R261" t="n">
-        <v>6827020</v>
+        <v>6826685</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27516,10 +27483,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>119580187</v>
+        <v>119580401</v>
       </c>
       <c r="B262" t="n">
-        <v>5189</v>
+        <v>79115</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27528,33 +27495,28 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>105930</v>
+        <v>229821</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P262" t="inlineStr">
         <is>
           <t>Rävtjärnen, Dlr</t>
@@ -27623,10 +27585,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>119580756</v>
+        <v>119581605</v>
       </c>
       <c r="B263" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27635,38 +27597,38 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>480596</v>
+        <v>480518</v>
       </c>
       <c r="R263" t="n">
-        <v>6826876</v>
+        <v>6826765</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27725,10 +27687,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>119581252</v>
+        <v>119580756</v>
       </c>
       <c r="B264" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27741,34 +27703,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>480579</v>
+        <v>480596</v>
       </c>
       <c r="R264" t="n">
-        <v>6826835</v>
+        <v>6826876</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27827,10 +27789,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>119582910</v>
+        <v>119578984</v>
       </c>
       <c r="B265" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27839,41 +27801,41 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>480778</v>
+        <v>480389</v>
       </c>
       <c r="R265" t="n">
-        <v>6826820</v>
+        <v>6827030</v>
       </c>
       <c r="S265" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -27900,19 +27862,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -27927,22 +27879,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>119578713</v>
+        <v>119581252</v>
       </c>
       <c r="B266" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27951,38 +27903,38 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>480386</v>
+        <v>480579</v>
       </c>
       <c r="R266" t="n">
-        <v>6826995</v>
+        <v>6826835</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28041,10 +27993,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>119582239</v>
+        <v>119581193</v>
       </c>
       <c r="B267" t="n">
-        <v>74638</v>
+        <v>91840</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28053,41 +28005,41 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>480668</v>
+        <v>480559</v>
       </c>
       <c r="R267" t="n">
-        <v>6826697</v>
+        <v>6826841</v>
       </c>
       <c r="S267" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -28114,9 +28066,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28131,22 +28093,22 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>119582030</v>
+        <v>119578655</v>
       </c>
       <c r="B268" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28159,37 +28121,37 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>480509</v>
+        <v>480324</v>
       </c>
       <c r="R268" t="n">
-        <v>6826812</v>
+        <v>6826985</v>
       </c>
       <c r="S268" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28216,19 +28178,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28243,22 +28195,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>119582533</v>
+        <v>119579998</v>
       </c>
       <c r="B269" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28267,38 +28219,38 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>480732</v>
+        <v>480486</v>
       </c>
       <c r="R269" t="n">
-        <v>6826736</v>
+        <v>6827011</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28357,10 +28309,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>119581465</v>
+        <v>119580187</v>
       </c>
       <c r="B270" t="n">
-        <v>78526</v>
+        <v>5189</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28369,38 +28321,43 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>480544</v>
+        <v>480542</v>
       </c>
       <c r="R270" t="n">
-        <v>6826825</v>
+        <v>6827033</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28459,10 +28416,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>119580401</v>
+        <v>119583661</v>
       </c>
       <c r="B271" t="n">
-        <v>79115</v>
+        <v>78526</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28475,37 +28432,37 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>480542</v>
+        <v>480558</v>
       </c>
       <c r="R271" t="n">
-        <v>6827033</v>
+        <v>6827045</v>
       </c>
       <c r="S271" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -28532,9 +28489,24 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA271" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>På talstam</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -28549,22 +28521,22 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>119578964</v>
+        <v>119582752</v>
       </c>
       <c r="B272" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28573,47 +28545,38 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>480378</v>
+        <v>480624</v>
       </c>
       <c r="R272" t="n">
-        <v>6827025</v>
+        <v>6826698</v>
       </c>
       <c r="S272" t="n">
         <v>9</v>
@@ -28645,7 +28608,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -28655,7 +28618,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -28682,10 +28645,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>119580910</v>
+        <v>119583148</v>
       </c>
       <c r="B273" t="n">
-        <v>79144</v>
+        <v>91832</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -28698,21 +28661,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -28722,10 +28685,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>480590</v>
+        <v>480684</v>
       </c>
       <c r="R273" t="n">
-        <v>6826836</v>
+        <v>6826961</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28784,10 +28747,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>119582035</v>
+        <v>119583044</v>
       </c>
       <c r="B274" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28796,38 +28759,38 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>480510</v>
+        <v>480711</v>
       </c>
       <c r="R274" t="n">
-        <v>6826812</v>
+        <v>6826881</v>
       </c>
       <c r="S274" t="n">
         <v>9</v>
@@ -28859,7 +28822,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -28869,7 +28832,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -28896,10 +28859,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>119579158</v>
+        <v>119582210</v>
       </c>
       <c r="B275" t="n">
-        <v>89633</v>
+        <v>91884</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -28912,37 +28875,46 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>480467</v>
+        <v>480495</v>
       </c>
       <c r="R275" t="n">
-        <v>6827000</v>
+        <v>6826796</v>
       </c>
       <c r="S275" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -28969,9 +28941,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -28986,22 +28968,22 @@
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>119581176</v>
+        <v>119580566</v>
       </c>
       <c r="B276" t="n">
-        <v>57310</v>
+        <v>91834</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -29014,42 +28996,46 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>480542</v>
+        <v>480597</v>
       </c>
       <c r="R276" t="n">
-        <v>6826841</v>
+        <v>6826933</v>
       </c>
       <c r="S276" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -29076,9 +29062,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -29093,22 +29089,22 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>119581193</v>
+        <v>119582425</v>
       </c>
       <c r="B277" t="n">
-        <v>91840</v>
+        <v>90580</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -29117,41 +29113,41 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>480559</v>
+        <v>480725</v>
       </c>
       <c r="R277" t="n">
-        <v>6826841</v>
+        <v>6826708</v>
       </c>
       <c r="S277" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -29178,19 +29174,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA277" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>12:53</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -29205,22 +29191,22 @@
       <c r="AT277" t="inlineStr"/>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>119579998</v>
+        <v>119582604</v>
       </c>
       <c r="B278" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -29229,41 +29215,41 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>480486</v>
+        <v>480554</v>
       </c>
       <c r="R278" t="n">
-        <v>6827011</v>
+        <v>6826774</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -29290,9 +29276,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -29307,22 +29303,22 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>119582581</v>
+        <v>119580285</v>
       </c>
       <c r="B279" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -29331,41 +29327,41 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>480554</v>
+        <v>480531</v>
       </c>
       <c r="R279" t="n">
-        <v>6826774</v>
+        <v>6827030</v>
       </c>
       <c r="S279" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -29392,19 +29388,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z279" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA279" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB279" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -29419,22 +29405,22 @@
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>119582604</v>
+        <v>119579902</v>
       </c>
       <c r="B280" t="n">
-        <v>57463</v>
+        <v>91834</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -29447,37 +29433,46 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>480554</v>
+        <v>480490</v>
       </c>
       <c r="R280" t="n">
-        <v>6826774</v>
+        <v>6827006</v>
       </c>
       <c r="S280" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -29506,7 +29501,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -29516,7 +29511,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -29543,10 +29538,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>119583661</v>
+        <v>119583506</v>
       </c>
       <c r="B281" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -29555,41 +29550,41 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>480558</v>
+        <v>480596</v>
       </c>
       <c r="R281" t="n">
-        <v>6827045</v>
+        <v>6827018</v>
       </c>
       <c r="S281" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -29616,24 +29611,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC281" t="inlineStr">
-        <is>
-          <t>På talstam</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -29648,22 +29628,22 @@
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>119578655</v>
+        <v>119582035</v>
       </c>
       <c r="B282" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -29676,37 +29656,37 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>480324</v>
+        <v>480510</v>
       </c>
       <c r="R282" t="n">
-        <v>6826985</v>
+        <v>6826812</v>
       </c>
       <c r="S282" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -29733,9 +29713,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA282" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -29750,22 +29740,22 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>119582896</v>
+        <v>119580002</v>
       </c>
       <c r="B283" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -29778,34 +29768,34 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>480697</v>
+        <v>480486</v>
       </c>
       <c r="R283" t="n">
-        <v>6826827</v>
+        <v>6827011</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29864,10 +29854,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>119579062</v>
+        <v>119578834</v>
       </c>
       <c r="B284" t="n">
-        <v>57310</v>
+        <v>78560</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -29880,42 +29870,37 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P284" t="inlineStr">
         <is>
           <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>480449</v>
+        <v>480414</v>
       </c>
       <c r="R284" t="n">
-        <v>6826994</v>
+        <v>6827025</v>
       </c>
       <c r="S284" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -29971,10 +29956,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>119583506</v>
+        <v>119581644</v>
       </c>
       <c r="B285" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -29983,25 +29968,25 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -30011,10 +29996,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>480596</v>
+        <v>480505</v>
       </c>
       <c r="R285" t="n">
-        <v>6827018</v>
+        <v>6826739</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -30073,7 +30058,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>119580285</v>
+        <v>119582910</v>
       </c>
       <c r="B286" t="n">
         <v>91840</v>
@@ -30109,17 +30094,17 @@
       <c r="I286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>480531</v>
+        <v>480778</v>
       </c>
       <c r="R286" t="n">
-        <v>6827030</v>
+        <v>6826820</v>
       </c>
       <c r="S286" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -30146,9 +30131,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA286" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -30163,22 +30158,22 @@
       <c r="AT286" t="inlineStr"/>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>119583227</v>
+        <v>119581176</v>
       </c>
       <c r="B287" t="n">
-        <v>78262</v>
+        <v>57310</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -30191,37 +30186,42 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>480664</v>
+        <v>480542</v>
       </c>
       <c r="R287" t="n">
-        <v>6826993</v>
+        <v>6826841</v>
       </c>
       <c r="S287" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -30248,19 +30248,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z287" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA287" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB287" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -30275,22 +30265,22 @@
       <c r="AT287" t="inlineStr"/>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>119581051</v>
+        <v>119582581</v>
       </c>
       <c r="B288" t="n">
-        <v>78262</v>
+        <v>91834</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -30303,37 +30293,37 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>480544</v>
+        <v>480554</v>
       </c>
       <c r="R288" t="n">
-        <v>6826852</v>
+        <v>6826774</v>
       </c>
       <c r="S288" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -30360,9 +30350,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA288" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -30377,22 +30377,22 @@
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>119582752</v>
+        <v>119581465</v>
       </c>
       <c r="B289" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -30401,41 +30401,41 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>480624</v>
+        <v>480544</v>
       </c>
       <c r="R289" t="n">
-        <v>6826698</v>
+        <v>6826825</v>
       </c>
       <c r="S289" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -30462,19 +30462,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z289" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA289" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -30489,22 +30479,22 @@
       <c r="AT289" t="inlineStr"/>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>119582623</v>
+        <v>119580549</v>
       </c>
       <c r="B290" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -30513,38 +30503,38 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>480770</v>
+        <v>480603</v>
       </c>
       <c r="R290" t="n">
-        <v>6826753</v>
+        <v>6826946</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -30603,10 +30593,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>119580002</v>
+        <v>119583019</v>
       </c>
       <c r="B291" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -30615,38 +30605,38 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>480486</v>
+        <v>480716</v>
       </c>
       <c r="R291" t="n">
-        <v>6827011</v>
+        <v>6826851</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -30705,10 +30695,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>119581581</v>
+        <v>119582950</v>
       </c>
       <c r="B292" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -30717,25 +30707,25 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
@@ -30745,10 +30735,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>480538</v>
+        <v>480695</v>
       </c>
       <c r="R292" t="n">
-        <v>6826770</v>
+        <v>6826849</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -30807,10 +30797,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>119580549</v>
+        <v>119582896</v>
       </c>
       <c r="B293" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -30819,38 +30809,38 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>480603</v>
+        <v>480697</v>
       </c>
       <c r="R293" t="n">
-        <v>6826946</v>
+        <v>6826827</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -30909,10 +30899,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>119579893</v>
+        <v>119580248</v>
       </c>
       <c r="B294" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -30921,41 +30911,50 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>480484</v>
+        <v>480513</v>
       </c>
       <c r="R294" t="n">
-        <v>6826991</v>
+        <v>6827030</v>
       </c>
       <c r="S294" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -30982,9 +30981,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z294" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA294" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB294" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -30999,22 +31008,22 @@
       <c r="AT294" t="inlineStr"/>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>119582028</v>
+        <v>119583227</v>
       </c>
       <c r="B295" t="n">
-        <v>91886</v>
+        <v>78262</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -31023,41 +31032,41 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>480596</v>
+        <v>480664</v>
       </c>
       <c r="R295" t="n">
-        <v>6826685</v>
+        <v>6826993</v>
       </c>
       <c r="S295" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -31084,9 +31093,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA295" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -31101,19 +31120,19 @@
       <c r="AT295" t="inlineStr"/>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>119582950</v>
+        <v>119580925</v>
       </c>
       <c r="B296" t="n">
         <v>91840</v>
@@ -31153,10 +31172,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>480695</v>
+        <v>480579</v>
       </c>
       <c r="R296" t="n">
-        <v>6826849</v>
+        <v>6826835</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -31215,10 +31234,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>119580248</v>
+        <v>119582239</v>
       </c>
       <c r="B297" t="n">
-        <v>91884</v>
+        <v>74638</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -31231,46 +31250,37 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>5449</v>
+        <v>6440</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>480513</v>
+        <v>480668</v>
       </c>
       <c r="R297" t="n">
-        <v>6827030</v>
+        <v>6826697</v>
       </c>
       <c r="S297" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>
@@ -31297,19 +31307,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z297" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA297" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB297" t="inlineStr">
-        <is>
-          <t>12:10</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -31324,22 +31324,22 @@
       <c r="AT297" t="inlineStr"/>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>119583148</v>
+        <v>119583130</v>
       </c>
       <c r="B298" t="n">
-        <v>91832</v>
+        <v>79643</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -31348,25 +31348,25 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>4361</v>
+        <v>6464</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -31438,10 +31438,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>119583130</v>
+        <v>119581581</v>
       </c>
       <c r="B299" t="n">
-        <v>79643</v>
+        <v>91884</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -31450,25 +31450,25 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>6464</v>
+        <v>5449</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
@@ -31478,10 +31478,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>480684</v>
+        <v>480538</v>
       </c>
       <c r="R299" t="n">
-        <v>6826961</v>
+        <v>6826770</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -31540,10 +31540,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>119581605</v>
+        <v>119581533</v>
       </c>
       <c r="B300" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -31556,21 +31556,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -31580,10 +31580,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>480518</v>
+        <v>480528</v>
       </c>
       <c r="R300" t="n">
-        <v>6826765</v>
+        <v>6826796</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -31642,10 +31642,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>119611873</v>
+        <v>119611877</v>
       </c>
       <c r="B301" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -31654,25 +31654,25 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -31682,10 +31682,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>480433</v>
+        <v>480597</v>
       </c>
       <c r="R301" t="n">
-        <v>6827020</v>
+        <v>6826814</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -31720,17 +31720,13 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC301" t="inlineStr">
-        <is>
-          <t>5 fkr</t>
-        </is>
-      </c>
       <c r="AD301" t="b">
         <v>0</v>
       </c>
       <c r="AE301" t="b">
         <v>0</v>
       </c>
+      <c r="AF301" t="inlineStr"/>
       <c r="AG301" t="b">
         <v>0</v>
       </c>
@@ -31749,10 +31745,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>119611400</v>
+        <v>119611865</v>
       </c>
       <c r="B302" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -31761,25 +31757,25 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -31789,10 +31785,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>480494</v>
+        <v>480563</v>
       </c>
       <c r="R302" t="n">
-        <v>6827013</v>
+        <v>6826868</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -31827,11 +31823,6 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC302" t="inlineStr">
-        <is>
-          <t>10-tal. 10 m punkt.  + svart tagg en fk.</t>
-        </is>
-      </c>
       <c r="AD302" t="b">
         <v>0</v>
       </c>
@@ -31845,12 +31836,12 @@
       <c r="AT302" t="inlineStr"/>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
@@ -31965,10 +31956,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>119611853</v>
+        <v>119611399</v>
       </c>
       <c r="B304" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -31977,38 +31968,38 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
-          <t>Rävtjärn norra, Dlr</t>
+          <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>480598</v>
+        <v>480492</v>
       </c>
       <c r="R304" t="n">
-        <v>6826815</v>
+        <v>6827011</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -32049,28 +32040,29 @@
       <c r="AE304" t="b">
         <v>0</v>
       </c>
+      <c r="AF304" t="inlineStr"/>
       <c r="AG304" t="b">
         <v>0</v>
       </c>
       <c r="AT304" t="inlineStr"/>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>119580822</v>
+        <v>119611397</v>
       </c>
       <c r="B305" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -32079,38 +32071,38 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>480579</v>
+        <v>480586</v>
       </c>
       <c r="R305" t="n">
-        <v>6826874</v>
+        <v>6826852</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -32145,34 +32137,40 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC305" t="inlineStr">
+        <is>
+          <t>Sex fk.</t>
+        </is>
+      </c>
       <c r="AD305" t="b">
         <v>0</v>
       </c>
       <c r="AE305" t="b">
         <v>0</v>
       </c>
+      <c r="AF305" t="inlineStr"/>
       <c r="AG305" t="b">
         <v>0</v>
       </c>
       <c r="AT305" t="inlineStr"/>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Lars-Erik Nilsson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>119611398</v>
+        <v>119611875</v>
       </c>
       <c r="B306" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -32181,25 +32179,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -32209,10 +32207,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>480325</v>
+        <v>480408</v>
       </c>
       <c r="R306" t="n">
-        <v>6826976</v>
+        <v>6827041</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -32247,6 +32245,11 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC306" t="inlineStr">
+        <is>
+          <t>5 fkr</t>
+        </is>
+      </c>
       <c r="AD306" t="b">
         <v>0</v>
       </c>
@@ -32259,22 +32262,22 @@
       <c r="AT306" t="inlineStr"/>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>119611877</v>
+        <v>119580822</v>
       </c>
       <c r="B307" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -32283,38 +32286,38 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
         <is>
-          <t>Rävtjärn, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>480597</v>
+        <v>480579</v>
       </c>
       <c r="R307" t="n">
-        <v>6826814</v>
+        <v>6826874</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -32355,29 +32358,28 @@
       <c r="AE307" t="b">
         <v>0</v>
       </c>
-      <c r="AF307" t="inlineStr"/>
       <c r="AG307" t="b">
         <v>0</v>
       </c>
       <c r="AT307" t="inlineStr"/>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>119611394</v>
+        <v>119611395</v>
       </c>
       <c r="B308" t="n">
-        <v>79115</v>
+        <v>91884</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -32390,21 +32392,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>229821</v>
+        <v>5449</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -32414,10 +32416,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>480388</v>
+        <v>480481</v>
       </c>
       <c r="R308" t="n">
-        <v>6827017</v>
+        <v>6827004</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -32458,6 +32460,7 @@
       <c r="AE308" t="b">
         <v>0</v>
       </c>
+      <c r="AF308" t="inlineStr"/>
       <c r="AG308" t="b">
         <v>0</v>
       </c>
@@ -32476,10 +32479,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>119611397</v>
+        <v>119611853</v>
       </c>
       <c r="B309" t="n">
-        <v>91844</v>
+        <v>78560</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -32488,38 +32491,38 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>4365</v>
+        <v>185</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Rävtjärn, Dlr</t>
+          <t>Rävtjärn norra, Dlr</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>480586</v>
+        <v>480598</v>
       </c>
       <c r="R309" t="n">
-        <v>6826852</v>
+        <v>6826815</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -32554,37 +32557,31 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC309" t="inlineStr">
-        <is>
-          <t>Sex fk.</t>
-        </is>
-      </c>
       <c r="AD309" t="b">
         <v>0</v>
       </c>
       <c r="AE309" t="b">
         <v>0</v>
       </c>
-      <c r="AF309" t="inlineStr"/>
       <c r="AG309" t="b">
         <v>0</v>
       </c>
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Bo karlstens</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>119611875</v>
+        <v>119611873</v>
       </c>
       <c r="B310" t="n">
         <v>91840</v>
@@ -32624,10 +32621,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>480408</v>
+        <v>480433</v>
       </c>
       <c r="R310" t="n">
-        <v>6827041</v>
+        <v>6827020</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -32691,10 +32688,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>119611865</v>
+        <v>119611400</v>
       </c>
       <c r="B311" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -32703,25 +32700,25 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -32731,10 +32728,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>480563</v>
+        <v>480494</v>
       </c>
       <c r="R311" t="n">
-        <v>6826868</v>
+        <v>6827013</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -32769,6 +32766,11 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>10-tal. 10 m punkt.  + svart tagg en fk.</t>
+        </is>
+      </c>
       <c r="AD311" t="b">
         <v>0</v>
       </c>
@@ -32782,22 +32784,22 @@
       <c r="AT311" t="inlineStr"/>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>119611395</v>
+        <v>119611398</v>
       </c>
       <c r="B312" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -32810,21 +32812,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
@@ -32834,10 +32836,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>480481</v>
+        <v>480325</v>
       </c>
       <c r="R312" t="n">
-        <v>6827004</v>
+        <v>6826976</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -32878,7 +32880,6 @@
       <c r="AE312" t="b">
         <v>0</v>
       </c>
-      <c r="AF312" t="inlineStr"/>
       <c r="AG312" t="b">
         <v>0</v>
       </c>
@@ -32897,10 +32898,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>119611399</v>
+        <v>119611394</v>
       </c>
       <c r="B313" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -32909,25 +32910,25 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
@@ -32937,10 +32938,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>480492</v>
+        <v>480388</v>
       </c>
       <c r="R313" t="n">
-        <v>6827011</v>
+        <v>6827017</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -32981,7 +32982,6 @@
       <c r="AE313" t="b">
         <v>0</v>
       </c>
-      <c r="AF313" t="inlineStr"/>
       <c r="AG313" t="b">
         <v>0</v>
       </c>
@@ -33000,10 +33000,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>119591274</v>
+        <v>119591268</v>
       </c>
       <c r="B314" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -33016,34 +33016,45 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I314" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="N314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
           <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>480538</v>
+        <v>480547</v>
       </c>
       <c r="R314" t="n">
-        <v>6826836</v>
+        <v>6826709</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -33084,6 +33095,7 @@
       <c r="AE314" t="b">
         <v>0</v>
       </c>
+      <c r="AF314" t="inlineStr"/>
       <c r="AG314" t="b">
         <v>0</v>
       </c>
@@ -33102,10 +33114,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>119591271</v>
+        <v>119591281</v>
       </c>
       <c r="B315" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -33118,21 +33130,21 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -33142,10 +33154,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>480649</v>
+        <v>480657</v>
       </c>
       <c r="R315" t="n">
-        <v>6826946</v>
+        <v>6826963</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>
@@ -33204,10 +33216,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>119591275</v>
+        <v>119591279</v>
       </c>
       <c r="B316" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -33216,25 +33228,25 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
@@ -33244,10 +33256,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>480440</v>
+        <v>480470</v>
       </c>
       <c r="R316" t="n">
-        <v>6826986</v>
+        <v>6826996</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -33306,10 +33318,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>119591281</v>
+        <v>119591266</v>
       </c>
       <c r="B317" t="n">
-        <v>91834</v>
+        <v>79115</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -33322,21 +33334,21 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
@@ -33346,10 +33358,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>480657</v>
+        <v>480508</v>
       </c>
       <c r="R317" t="n">
-        <v>6826963</v>
+        <v>6826822</v>
       </c>
       <c r="S317" t="n">
         <v>10</v>
@@ -33408,7 +33420,7 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>119591276</v>
+        <v>119591271</v>
       </c>
       <c r="B318" t="n">
         <v>78526</v>
@@ -33448,10 +33460,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>480354</v>
+        <v>480649</v>
       </c>
       <c r="R318" t="n">
-        <v>6826995</v>
+        <v>6826946</v>
       </c>
       <c r="S318" t="n">
         <v>10</v>
@@ -33510,7 +33522,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>119591272</v>
+        <v>119591276</v>
       </c>
       <c r="B319" t="n">
         <v>78526</v>
@@ -33550,10 +33562,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>480462</v>
+        <v>480354</v>
       </c>
       <c r="R319" t="n">
-        <v>6826804</v>
+        <v>6826995</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -33726,10 +33738,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>119591268</v>
+        <v>119591278</v>
       </c>
       <c r="B321" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -33738,49 +33750,38 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
           <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>480547</v>
+        <v>480579</v>
       </c>
       <c r="R321" t="n">
-        <v>6826709</v>
+        <v>6826701</v>
       </c>
       <c r="S321" t="n">
         <v>10</v>
@@ -33821,7 +33822,6 @@
       <c r="AE321" t="b">
         <v>0</v>
       </c>
-      <c r="AF321" t="inlineStr"/>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
@@ -33840,10 +33840,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>119591269</v>
+        <v>119591275</v>
       </c>
       <c r="B322" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -33856,21 +33856,21 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
@@ -33880,10 +33880,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>480496</v>
+        <v>480440</v>
       </c>
       <c r="R322" t="n">
-        <v>6826816</v>
+        <v>6826986</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -33942,10 +33942,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>119591278</v>
+        <v>119591274</v>
       </c>
       <c r="B323" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -33954,25 +33954,25 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
@@ -33982,10 +33982,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>480579</v>
+        <v>480538</v>
       </c>
       <c r="R323" t="n">
-        <v>6826701</v>
+        <v>6826836</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -34044,10 +34044,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>119591279</v>
+        <v>119591269</v>
       </c>
       <c r="B324" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -34056,25 +34056,25 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
@@ -34084,10 +34084,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>480470</v>
+        <v>480496</v>
       </c>
       <c r="R324" t="n">
-        <v>6826996</v>
+        <v>6826816</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -34146,10 +34146,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>119591273</v>
+        <v>119591267</v>
       </c>
       <c r="B325" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -34162,21 +34162,21 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
@@ -34186,10 +34186,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>480540</v>
+        <v>480551</v>
       </c>
       <c r="R325" t="n">
-        <v>6826733</v>
+        <v>6826709</v>
       </c>
       <c r="S325" t="n">
         <v>10</v>
@@ -34248,10 +34248,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>119591267</v>
+        <v>119591273</v>
       </c>
       <c r="B326" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -34264,21 +34264,21 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
@@ -34288,10 +34288,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>480551</v>
+        <v>480540</v>
       </c>
       <c r="R326" t="n">
-        <v>6826709</v>
+        <v>6826733</v>
       </c>
       <c r="S326" t="n">
         <v>10</v>
@@ -34350,10 +34350,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>119591266</v>
+        <v>119591272</v>
       </c>
       <c r="B327" t="n">
-        <v>79115</v>
+        <v>78526</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -34366,21 +34366,21 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
@@ -34390,10 +34390,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>480508</v>
+        <v>480462</v>
       </c>
       <c r="R327" t="n">
-        <v>6826822</v>
+        <v>6826804</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -34452,10 +34452,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>119672813</v>
+        <v>119672823</v>
       </c>
       <c r="B328" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -34464,25 +34464,25 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
@@ -34492,10 +34492,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>480548</v>
+        <v>480476</v>
       </c>
       <c r="R328" t="n">
-        <v>6826709</v>
+        <v>6827006</v>
       </c>
       <c r="S328" t="n">
         <v>1</v>
@@ -34554,10 +34554,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>119672823</v>
+        <v>119672815</v>
       </c>
       <c r="B329" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -34566,25 +34566,25 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
@@ -34597,7 +34597,7 @@
         <v>480476</v>
       </c>
       <c r="R329" t="n">
-        <v>6827006</v>
+        <v>6827010</v>
       </c>
       <c r="S329" t="n">
         <v>1</v>
@@ -34656,10 +34656,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>119672814</v>
+        <v>119672822</v>
       </c>
       <c r="B330" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -34668,25 +34668,25 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -34696,10 +34696,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>480675</v>
+        <v>480507</v>
       </c>
       <c r="R330" t="n">
-        <v>6826761</v>
+        <v>6827003</v>
       </c>
       <c r="S330" t="n">
         <v>1</v>
@@ -34758,7 +34758,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>119672821</v>
+        <v>119672820</v>
       </c>
       <c r="B331" t="n">
         <v>91840</v>
@@ -34798,10 +34798,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>480566</v>
+        <v>480670</v>
       </c>
       <c r="R331" t="n">
-        <v>6826703</v>
+        <v>6826723</v>
       </c>
       <c r="S331" t="n">
         <v>1</v>
@@ -34860,10 +34860,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>119672811</v>
+        <v>119672814</v>
       </c>
       <c r="B332" t="n">
-        <v>91844</v>
+        <v>78262</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -34872,25 +34872,25 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
@@ -34900,10 +34900,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>480600</v>
+        <v>480675</v>
       </c>
       <c r="R332" t="n">
-        <v>6826809</v>
+        <v>6826761</v>
       </c>
       <c r="S332" t="n">
         <v>1</v>
@@ -34938,11 +34938,6 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC332" t="inlineStr">
-        <is>
-          <t>Timmergröppa</t>
-        </is>
-      </c>
       <c r="AD332" t="b">
         <v>0</v>
       </c>
@@ -34960,17 +34955,17 @@
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>Erik Danielsson, Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>119672810</v>
+        <v>119672821</v>
       </c>
       <c r="B333" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -34979,25 +34974,25 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
@@ -35007,10 +35002,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>480583</v>
+        <v>480566</v>
       </c>
       <c r="R333" t="n">
-        <v>6826837</v>
+        <v>6826703</v>
       </c>
       <c r="S333" t="n">
         <v>1</v>
@@ -35171,10 +35166,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>119672820</v>
+        <v>119672811</v>
       </c>
       <c r="B335" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -35183,25 +35178,25 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
@@ -35211,10 +35206,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>480670</v>
+        <v>480600</v>
       </c>
       <c r="R335" t="n">
-        <v>6826723</v>
+        <v>6826809</v>
       </c>
       <c r="S335" t="n">
         <v>1</v>
@@ -35249,6 +35244,11 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>Timmergröppa</t>
+        </is>
+      </c>
       <c r="AD335" t="b">
         <v>0</v>
       </c>
@@ -35266,17 +35266,17 @@
       </c>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Erik Danielsson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>119672815</v>
+        <v>119672806</v>
       </c>
       <c r="B336" t="n">
-        <v>78262</v>
+        <v>56522</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -35285,25 +35285,25 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
@@ -35313,10 +35313,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>480476</v>
+        <v>480319</v>
       </c>
       <c r="R336" t="n">
-        <v>6827010</v>
+        <v>6826995</v>
       </c>
       <c r="S336" t="n">
         <v>1</v>
@@ -35349,6 +35349,11 @@
       <c r="AA336" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC336" t="inlineStr">
+        <is>
+          <t>myllgrop</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -35375,10 +35380,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>119672818</v>
+        <v>119672810</v>
       </c>
       <c r="B337" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -35387,25 +35392,25 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -35415,10 +35420,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>480668</v>
+        <v>480583</v>
       </c>
       <c r="R337" t="n">
-        <v>6826904</v>
+        <v>6826837</v>
       </c>
       <c r="S337" t="n">
         <v>1</v>
@@ -35477,10 +35482,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>119672822</v>
+        <v>119672813</v>
       </c>
       <c r="B338" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -35489,25 +35494,25 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -35517,10 +35522,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>480507</v>
+        <v>480548</v>
       </c>
       <c r="R338" t="n">
-        <v>6827003</v>
+        <v>6826709</v>
       </c>
       <c r="S338" t="n">
         <v>1</v>
@@ -35579,10 +35584,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>119672806</v>
+        <v>119672818</v>
       </c>
       <c r="B339" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -35595,21 +35600,21 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -35619,10 +35624,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>480319</v>
+        <v>480668</v>
       </c>
       <c r="R339" t="n">
-        <v>6826995</v>
+        <v>6826904</v>
       </c>
       <c r="S339" t="n">
         <v>1</v>
@@ -35655,11 +35660,6 @@
       <c r="AA339" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC339" t="inlineStr">
-        <is>
-          <t>myllgrop</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -35788,10 +35788,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>119710922</v>
+        <v>119710927</v>
       </c>
       <c r="B341" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -35804,21 +35804,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
@@ -35828,10 +35828,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>480596</v>
+        <v>480320</v>
       </c>
       <c r="R341" t="n">
-        <v>6826803</v>
+        <v>6826981</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -35890,10 +35890,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>119710926</v>
+        <v>119710917</v>
       </c>
       <c r="B342" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -35906,21 +35906,21 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
@@ -35930,10 +35930,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>480595</v>
+        <v>480550</v>
       </c>
       <c r="R342" t="n">
-        <v>6826798</v>
+        <v>6826865</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -35974,6 +35974,7 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
+      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
@@ -35992,10 +35993,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>119710917</v>
+        <v>119710925</v>
       </c>
       <c r="B343" t="n">
-        <v>78560</v>
+        <v>78262</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -36008,21 +36009,21 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
@@ -36032,10 +36033,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>480550</v>
+        <v>480604</v>
       </c>
       <c r="R343" t="n">
-        <v>6826865</v>
+        <v>6826853</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -36076,7 +36077,6 @@
       <c r="AE343" t="b">
         <v>0</v>
       </c>
-      <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="b">
         <v>0</v>
       </c>
@@ -36095,10 +36095,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>119710925</v>
+        <v>119710922</v>
       </c>
       <c r="B344" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -36111,21 +36111,21 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
@@ -36135,10 +36135,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>480604</v>
+        <v>480596</v>
       </c>
       <c r="R344" t="n">
-        <v>6826853</v>
+        <v>6826803</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -36197,10 +36197,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>119710927</v>
+        <v>119710923</v>
       </c>
       <c r="B345" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -36213,21 +36213,21 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
@@ -36237,10 +36237,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>480320</v>
+        <v>480600</v>
       </c>
       <c r="R345" t="n">
-        <v>6826981</v>
+        <v>6826807</v>
       </c>
       <c r="S345" t="n">
         <v>10</v>
@@ -36299,10 +36299,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>119710918</v>
+        <v>119710915</v>
       </c>
       <c r="B346" t="n">
-        <v>56522</v>
+        <v>78560</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -36311,50 +36311,38 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr"/>
-      <c r="L346" t="inlineStr"/>
-      <c r="M346" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N346" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
           <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>480604</v>
+        <v>480558</v>
       </c>
       <c r="R346" t="n">
-        <v>6826853</v>
+        <v>6826871</v>
       </c>
       <c r="S346" t="n">
         <v>10</v>
@@ -36413,10 +36401,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>119710915</v>
+        <v>119710926</v>
       </c>
       <c r="B347" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -36429,21 +36417,21 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
@@ -36453,10 +36441,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>480558</v>
+        <v>480595</v>
       </c>
       <c r="R347" t="n">
-        <v>6826871</v>
+        <v>6826798</v>
       </c>
       <c r="S347" t="n">
         <v>10</v>
@@ -36515,10 +36503,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>119710924</v>
+        <v>119710929</v>
       </c>
       <c r="B348" t="n">
-        <v>79607</v>
+        <v>91834</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -36531,21 +36519,21 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
@@ -36555,10 +36543,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>480688</v>
+        <v>480555</v>
       </c>
       <c r="R348" t="n">
-        <v>6826928</v>
+        <v>6826871</v>
       </c>
       <c r="S348" t="n">
         <v>10</v>
@@ -36617,10 +36605,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>119710929</v>
+        <v>119710918</v>
       </c>
       <c r="B349" t="n">
-        <v>91834</v>
+        <v>56522</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -36629,38 +36617,50 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I349" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr"/>
       <c r="P349" t="inlineStr">
         <is>
           <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>480555</v>
+        <v>480604</v>
       </c>
       <c r="R349" t="n">
-        <v>6826871</v>
+        <v>6826853</v>
       </c>
       <c r="S349" t="n">
         <v>10</v>
@@ -36719,10 +36719,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>119710928</v>
+        <v>119710924</v>
       </c>
       <c r="B350" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -36731,25 +36731,25 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I350" t="inlineStr"/>
@@ -36759,10 +36759,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>480598</v>
+        <v>480688</v>
       </c>
       <c r="R350" t="n">
-        <v>6826836</v>
+        <v>6826928</v>
       </c>
       <c r="S350" t="n">
         <v>10</v>
@@ -36821,10 +36821,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>119710923</v>
+        <v>119710914</v>
       </c>
       <c r="B351" t="n">
-        <v>78263</v>
+        <v>78560</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -36837,21 +36837,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I351" t="inlineStr"/>
@@ -36861,10 +36861,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>480600</v>
+        <v>480608</v>
       </c>
       <c r="R351" t="n">
-        <v>6826807</v>
+        <v>6826848</v>
       </c>
       <c r="S351" t="n">
         <v>10</v>
@@ -36923,10 +36923,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>119710914</v>
+        <v>119710928</v>
       </c>
       <c r="B352" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -36935,25 +36935,25 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
@@ -36963,10 +36963,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>480608</v>
+        <v>480598</v>
       </c>
       <c r="R352" t="n">
-        <v>6826848</v>
+        <v>6826836</v>
       </c>
       <c r="S352" t="n">
         <v>10</v>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -32479,10 +32479,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>119611853</v>
+        <v>119611873</v>
       </c>
       <c r="B309" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -32491,38 +32491,38 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Rävtjärn norra, Dlr</t>
+          <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>480598</v>
+        <v>480433</v>
       </c>
       <c r="R309" t="n">
-        <v>6826815</v>
+        <v>6827020</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -32555,6 +32555,11 @@
       <c r="AA309" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>5 fkr</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -32581,10 +32586,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>119611873</v>
+        <v>119611853</v>
       </c>
       <c r="B310" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -32593,38 +32598,38 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Rävtjärn, Dlr</t>
+          <t>Rävtjärn norra, Dlr</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>480433</v>
+        <v>480598</v>
       </c>
       <c r="R310" t="n">
-        <v>6827020</v>
+        <v>6826815</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -32657,11 +32662,6 @@
       <c r="AA310" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC310" t="inlineStr">
-        <is>
-          <t>5 fkr</t>
         </is>
       </c>
       <c r="AD310" t="b">

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -33738,10 +33738,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>119591278</v>
+        <v>119591275</v>
       </c>
       <c r="B321" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -33750,25 +33750,25 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
@@ -33778,10 +33778,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>480579</v>
+        <v>480440</v>
       </c>
       <c r="R321" t="n">
-        <v>6826701</v>
+        <v>6826986</v>
       </c>
       <c r="S321" t="n">
         <v>10</v>
@@ -33840,10 +33840,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>119591275</v>
+        <v>119591278</v>
       </c>
       <c r="B322" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -33852,25 +33852,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
@@ -33880,10 +33880,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>480440</v>
+        <v>480579</v>
       </c>
       <c r="R322" t="n">
-        <v>6826986</v>
+        <v>6826701</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -26525,7 +26525,7 @@
         <v>119579062</v>
       </c>
       <c r="B253" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>119581176</v>
       </c>
       <c r="B287" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -26525,7 +26525,7 @@
         <v>119579062</v>
       </c>
       <c r="B253" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>119581176</v>
       </c>
       <c r="B287" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY352"/>
+  <dimension ref="A1:AY353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37023,6 +37023,107 @@
       </c>
       <c r="AY352" t="inlineStr"/>
     </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>128540013</v>
+      </c>
+      <c r="B353" t="n">
+        <v>92746</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q353" t="n">
+        <v>480322</v>
+      </c>
+      <c r="R353" t="n">
+        <v>6826983</v>
+      </c>
+      <c r="S353" t="n">
+        <v>10</v>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD353" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE353" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF353" t="inlineStr"/>
+      <c r="AG353" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT353" t="inlineStr"/>
+      <c r="AW353" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX353" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY353" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -37028,7 +37028,7 @@
         <v>128540013</v>
       </c>
       <c r="B353" t="n">
-        <v>92746</v>
+        <v>92752</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -37028,7 +37028,7 @@
         <v>128540013</v>
       </c>
       <c r="B353" t="n">
-        <v>92752</v>
+        <v>92758</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -37028,7 +37028,7 @@
         <v>128540013</v>
       </c>
       <c r="B353" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -37028,7 +37028,7 @@
         <v>128540013</v>
       </c>
       <c r="B353" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -37028,7 +37028,7 @@
         <v>128540013</v>
       </c>
       <c r="B353" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -37028,7 +37028,7 @@
         <v>128540013</v>
       </c>
       <c r="B353" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -37028,7 +37028,7 @@
         <v>128540013</v>
       </c>
       <c r="B353" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -37028,7 +37028,7 @@
         <v>128540013</v>
       </c>
       <c r="B353" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -37028,7 +37028,7 @@
         <v>128540013</v>
       </c>
       <c r="B353" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -37028,7 +37028,7 @@
         <v>128540013</v>
       </c>
       <c r="B353" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -37028,7 +37028,7 @@
         <v>128540013</v>
       </c>
       <c r="B353" t="n">
-        <v>92815</v>
+        <v>92823</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>

--- a/artfynd/A 30017-2024 artfynd.xlsx
+++ b/artfynd/A 30017-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY378"/>
+  <dimension ref="A1:AZ378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548719</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548600</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548601</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548602</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548603</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548604</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548605</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548606</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548607</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548608</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548609</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548610</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548611</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548612</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548613</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548614</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548615</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548616</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548617</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548618</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548619</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548620</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548621</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548622</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3102,6 +3227,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548623</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,6 +3329,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548624</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3296,6 +3431,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548625</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548626</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3490,6 +3635,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548627</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3587,6 +3737,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548628</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3684,6 +3839,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548630</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3781,6 +3941,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548631</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3878,6 +4043,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119578834</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3975,6 +4145,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582533</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4072,6 +4247,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611853</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4170,6 +4350,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611865</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4268,6 +4453,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611877</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4365,6 +4555,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710914</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4462,6 +4657,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710915</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4560,6 +4760,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710916</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4658,6 +4863,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710917</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4755,6 +4965,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548987</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4852,6 +5067,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548988</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4949,6 +5169,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548989</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5046,6 +5271,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548990</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5143,6 +5373,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548991</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5240,6 +5475,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548992</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5337,6 +5577,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548993</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5434,6 +5679,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548994</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5531,6 +5781,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548995</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5628,6 +5883,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548996</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5725,6 +5985,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548998</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5822,6 +6087,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548999</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5919,6 +6189,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549000</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6016,6 +6291,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549001</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6113,6 +6393,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549002</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6210,6 +6495,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549003</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6307,6 +6597,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549004</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6404,6 +6699,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549005</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6501,6 +6801,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549006</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6598,6 +6903,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549007</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6695,6 +7005,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549008</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6792,6 +7107,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549009</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6889,6 +7209,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549011</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6986,6 +7311,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549012</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7083,6 +7413,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549014</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7180,6 +7515,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549015</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7277,6 +7617,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548755</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7374,6 +7719,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548756</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7471,6 +7821,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548757</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7568,6 +7923,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119579158</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7675,6 +8035,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580686</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7772,6 +8137,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119581710</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7888,6 +8258,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119578964</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7985,6 +8360,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591267</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8082,6 +8462,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119583148</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8191,6 +8576,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591268</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8288,6 +8678,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672813</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8385,6 +8780,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549036</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8482,6 +8882,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549037</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8598,6 +9003,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119579902</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8695,6 +9105,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580002</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8811,6 +9226,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580034</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8927,6 +9347,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580566</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9043,6 +9468,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580851</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9150,6 +9580,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582581</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9247,6 +9682,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591281</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9344,6 +9784,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710929</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9450,6 +9895,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548929</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9556,6 +10006,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548930</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9662,6 +10117,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548934</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9768,6 +10228,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548935</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9874,6 +10339,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548936</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9980,6 +10450,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548938</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10086,6 +10561,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548939</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10192,6 +10672,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548941</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10298,6 +10783,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548942</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10404,6 +10894,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548943</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10510,6 +11005,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548944</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10616,6 +11116,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548945</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10722,6 +11227,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548946</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10828,6 +11338,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548947</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10934,6 +11449,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548949</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11040,6 +11560,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548950</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11146,6 +11671,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548951</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11252,6 +11782,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548952</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11358,6 +11893,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548953</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11464,6 +12004,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548954</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11570,6 +12115,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548955</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11676,6 +12226,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548956</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11782,6 +12337,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548958</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11879,6 +12439,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548960</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11976,6 +12541,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548961</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12073,6 +12643,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548962</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12170,6 +12745,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548963</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12267,6 +12847,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548964</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12364,6 +12949,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548965</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12461,6 +13051,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548966</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12558,6 +13153,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548967</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12655,6 +13255,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548968</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12752,6 +13357,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548969</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12849,6 +13459,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548970</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12946,6 +13561,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548971</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13043,6 +13663,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548972</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13149,6 +13774,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548975</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13246,6 +13876,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548977</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13343,6 +13978,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119579893</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13440,6 +14080,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119579998</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13537,6 +14182,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580285</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13634,6 +14284,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580549</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13731,6 +14386,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580637</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13828,6 +14488,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580756</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13925,6 +14590,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580822</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14032,6 +14702,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580883</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14129,6 +14804,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580925</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14236,6 +14916,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119581193</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14333,6 +15018,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119581402</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14440,6 +15130,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582752</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14547,6 +15242,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582910</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14644,6 +15344,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582950</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14741,6 +15446,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119583019</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14848,6 +15558,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119583044</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14955,6 +15670,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119583116</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15062,6 +15782,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119583384</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15159,6 +15884,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119583506</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15268,6 +15998,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591277</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15365,6 +16100,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591278</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15462,6 +16202,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591279</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15560,6 +16305,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611399</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15663,6 +16413,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611400</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15765,6 +16520,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611873</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15867,6 +16627,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611875</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15964,6 +16729,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672818</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16061,6 +16831,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672819</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16158,6 +16933,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672820</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16255,6 +17035,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672821</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16352,6 +17137,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672822</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16449,6 +17239,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672823</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16546,6 +17341,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672824</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16643,6 +17443,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672825</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16740,6 +17545,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710928</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16843,6 +17653,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611397</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16945,6 +17760,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672811</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17046,6 +17866,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128540013</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17143,6 +17968,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548726</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17240,6 +18070,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548727</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17337,6 +18172,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119581252</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17434,6 +18274,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548707</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17531,6 +18376,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548708</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17628,6 +18478,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548709</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17735,6 +18590,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119578633</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17832,6 +18692,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548731</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17929,6 +18794,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548733</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18026,6 +18896,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548734</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18123,6 +18998,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548781</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18220,6 +19100,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548782</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18317,6 +19202,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548783</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18414,6 +19304,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548784</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18511,6 +19406,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548785</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18608,6 +19508,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548786</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18705,6 +19610,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548787</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18802,6 +19712,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548789</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18899,6 +19814,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548790</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18996,6 +19916,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548791</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19093,6 +20018,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548793</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19190,6 +20120,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548794</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19287,6 +20222,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548795</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19384,6 +20324,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548796</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19481,6 +20426,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548798</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19578,6 +20528,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548799</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19675,6 +20630,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548800</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19772,6 +20732,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548801</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19869,6 +20834,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548802</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19966,6 +20936,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548803</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20063,6 +21038,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548804</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20160,6 +21140,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548805</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20257,6 +21242,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548806</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20354,6 +21344,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548807</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20451,6 +21446,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548808</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20548,6 +21548,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548809</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20645,6 +21650,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548810</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20742,6 +21752,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548811</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20839,6 +21854,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548812</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20936,6 +21956,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548813</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21033,6 +22058,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548814</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21130,6 +22160,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548815</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21227,6 +22262,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548816</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21324,6 +22364,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548817</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21421,6 +22466,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548820</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21518,6 +22568,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548821</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21615,6 +22670,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548822</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21712,6 +22772,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548823</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21809,6 +22874,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548824</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21906,6 +22976,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548825</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22003,6 +23078,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548826</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22100,6 +23180,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548827</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22197,6 +23282,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548828</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22294,6 +23384,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548829</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22391,6 +23486,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548830</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22488,6 +23588,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548831</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22585,6 +23690,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548832</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22682,6 +23792,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548834</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22779,6 +23894,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548835</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -22876,6 +23996,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548837</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -22973,6 +24098,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548838</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23070,6 +24200,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548839</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23167,6 +24302,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548840</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23264,6 +24404,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548841</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23361,6 +24506,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548842</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23458,6 +24608,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548843</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23555,6 +24710,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548845</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23652,6 +24812,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548846</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23749,6 +24914,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548847</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23846,6 +25016,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548848</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -23943,6 +25118,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548849</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24040,6 +25220,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548850</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24137,6 +25322,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548851</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24234,6 +25424,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548852</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24331,6 +25526,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548853</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24428,6 +25628,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548854</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24525,6 +25730,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548855</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24622,6 +25832,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548856</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24719,6 +25934,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548857</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -24816,6 +26036,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548858</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -24913,6 +26138,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548860</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25010,6 +26240,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548862</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25107,6 +26342,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548863</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25204,6 +26444,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548864</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25301,6 +26546,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548865</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25398,6 +26648,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548866</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25495,6 +26750,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548867</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25592,6 +26852,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548868</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25689,6 +26954,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548869</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -25786,6 +27056,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548870</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -25883,6 +27158,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548871</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -25980,6 +27260,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548872</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -26077,6 +27362,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548873</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -26174,6 +27464,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548874</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26271,6 +27566,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548875</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26368,6 +27668,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548876</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26465,6 +27770,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548877</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -26562,6 +27872,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548878</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -26659,6 +27974,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548879</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -26756,6 +28076,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548880</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -26853,6 +28178,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548882</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -26950,6 +28280,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548883</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -27047,6 +28382,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548884</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -27144,6 +28484,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548885</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -27241,6 +28586,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548886</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -27338,6 +28688,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548887</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -27435,6 +28790,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548888</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -27532,6 +28892,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548889</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -27629,6 +28994,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548890</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -27726,6 +29096,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548891</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -27823,6 +29198,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548892</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -27920,6 +29300,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548893</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -28017,6 +29402,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548895</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -28114,6 +29504,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548896</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -28211,6 +29606,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548897</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -28308,6 +29708,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548898</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -28405,6 +29810,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548899</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -28502,6 +29912,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548900</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -28599,6 +30014,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548901</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -28696,6 +30116,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548902</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -28793,6 +30218,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548903</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -28890,6 +30320,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548904</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -28987,6 +30422,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548905</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -29084,6 +30524,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548906</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -29181,6 +30626,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548908</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -29278,6 +30728,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548926</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -29375,6 +30830,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119578655</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -29472,6 +30932,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119578713</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -29569,6 +31034,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119581465</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -29666,6 +31136,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119581533</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -29763,6 +31238,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119581644</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -29860,6 +31340,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582623</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -29957,6 +31442,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582896</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -30054,6 +31544,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119583220</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -30166,6 +31661,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119583661</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -30263,6 +31763,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591271</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -30360,6 +31865,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591272</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -30457,6 +31967,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591273</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -30554,6 +32069,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591274</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -30651,6 +32171,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591275</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -30748,6 +32273,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591276</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -30845,6 +32375,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611398</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -30942,6 +32477,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710926</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -31039,6 +32579,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710927</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -31136,6 +32681,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580684</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -31233,6 +32783,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582239</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -31330,6 +32885,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582455</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -31427,6 +32987,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548746</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -31524,6 +33089,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548747</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -31621,6 +33191,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548748</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -31718,6 +33293,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119579045</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -31815,6 +33395,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580118</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -31912,6 +33497,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119581051</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -32019,6 +33609,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582030</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -32126,6 +33721,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119583227</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -32223,6 +33823,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591270</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -32320,6 +33925,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672814</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -32417,6 +34027,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672815</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -32514,6 +34129,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710925</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -32611,6 +34231,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548652</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -32708,6 +34333,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548653</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -32805,6 +34435,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548654</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -32902,6 +34537,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548655</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -32999,6 +34639,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548656</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -33096,6 +34741,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548657</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -33193,6 +34843,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548659</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -33290,6 +34945,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548660</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -33387,6 +35047,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548661</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -33484,6 +35149,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548662</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -33581,6 +35251,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548663</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -33678,6 +35353,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548664</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -33775,6 +35455,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548665</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -33872,6 +35557,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548666</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -33969,6 +35659,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548667</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -34066,6 +35761,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548668</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -34163,6 +35863,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548669</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -34260,6 +35965,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548671</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -34357,6 +36067,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548672</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -34454,6 +36169,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548673</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -34551,6 +36271,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580536</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -34648,6 +36373,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580910</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -34745,6 +36475,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119581605</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -34842,6 +36577,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710924</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -34939,6 +36679,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119583130</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -35041,6 +36786,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119579062</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -35143,6 +36893,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119581176</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -35240,6 +36995,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548698</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -35342,6 +37102,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672806</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -35451,6 +37216,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710918</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -35548,6 +37318,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548753</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -35649,6 +37424,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548700</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -35746,6 +37526,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548701</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -35843,6 +37628,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548702</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -35940,6 +37730,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548704</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -36037,6 +37832,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548705</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -36144,6 +37944,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582604</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -36246,6 +38051,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580187</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -36353,6 +38163,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119583482</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -36450,6 +38265,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548736</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -36557,6 +38377,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582035</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -36654,6 +38479,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591269</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -36751,6 +38581,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710922</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -36848,6 +38683,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710923</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -36945,6 +38785,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548692</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -37042,6 +38887,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548693</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -37139,6 +38989,11 @@
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548694</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -37236,6 +39091,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548695</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -37333,6 +39193,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119580401</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -37430,6 +39295,11 @@
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591266</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -37527,6 +39397,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611394</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -37624,6 +39499,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119582028</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -37721,6 +39601,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119672807</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -37818,8 +39703,392 @@
         </is>
       </c>
       <c r="AY378" t="inlineStr"/>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710920</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>